--- a/SandBox/maps/Collaborators.xlsx
+++ b/SandBox/maps/Collaborators.xlsx
@@ -157,7 +157,7 @@
     <t xml:space="preserve">Cardiff University</t>
   </si>
   <si>
-    <t xml:space="preserve">zxcv</t>
+    <t xml:space="preserve">Cardiff</t>
   </si>
   <si>
     <t xml:space="preserve">Wales</t>
@@ -303,11 +303,11 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H16"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="36.45"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14.62"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13.93"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13.93"/>
   </cols>

--- a/SandBox/maps/Collaborators.xlsx
+++ b/SandBox/maps/Collaborators.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25730"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="263" documentId="11_2783B361715DD81B2B2E30CD8B5EBE776678445D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1209B148-F7F7-475F-8222-181DBBB44A07}"/>
+  <xr:revisionPtr revIDLastSave="288" documentId="11_2783B361715DD81B2B2E30CD8B5EBE776678445D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6873FBE2-AAD3-439F-BEA1-6A20828423E9}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="148">
   <si>
     <t>Institution</t>
   </si>
@@ -69,6 +69,12 @@
     <t>Rachel Quinlan</t>
   </si>
   <si>
+    <t>Chinese Academy of Sciences</t>
+  </si>
+  <si>
+    <t>Niall Madden</t>
+  </si>
+  <si>
     <t>City University of Hong Kong</t>
   </si>
   <si>
@@ -87,9 +93,6 @@
     <t>Computational Science Research Center</t>
   </si>
   <si>
-    <t>Niall Madden</t>
-  </si>
-  <si>
     <t>Cooch Behar Panchanan Barma University</t>
   </si>
   <si>
@@ -186,6 +189,12 @@
     <t>London</t>
   </si>
   <si>
+    <t>Maynooth University</t>
+  </si>
+  <si>
+    <t>Kildare</t>
+  </si>
+  <si>
     <t>Memorial University of Newfoundland</t>
   </si>
   <si>
@@ -255,6 +264,12 @@
     <t>Austria</t>
   </si>
   <si>
+    <t>Technical University of Dublin</t>
+  </si>
+  <si>
+    <t>Trinity College Dublin</t>
+  </si>
+  <si>
     <t>Tufts Univerity</t>
   </si>
   <si>
@@ -454,12 +469,6 @@
   </si>
   <si>
     <t>Zaragoza</t>
-  </si>
-  <si>
-    <t>Veterinary Hospital</t>
-  </si>
-  <si>
-    <t>Fregis</t>
   </si>
   <si>
     <t>Zhejiang University</t>
@@ -472,7 +481,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -492,25 +501,6 @@
       <b/>
       <sz val="11"/>
       <name val="Cambria"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Cambria"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF444444"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF4D5156"/>
-      <name val="Arial"/>
-      <family val="2"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -549,17 +539,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -874,7 +859,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="36.42578125" customWidth="1"/>
@@ -911,7 +896,7 @@
       <c r="C2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -933,14 +918,14 @@
       <c r="A4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>13</v>
+      <c r="B4" t="s">
+        <v>5</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>7</v>
+      <c r="D4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15">
@@ -951,24 +936,24 @@
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15">
       <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
         <v>17</v>
       </c>
-      <c r="B6" t="s">
-        <v>5</v>
-      </c>
       <c r="C6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="3" t="s">
         <v>18</v>
+      </c>
+      <c r="D6" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15">
@@ -976,240 +961,243 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>18</v>
+        <v>6</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15">
       <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
         <v>22</v>
       </c>
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>18</v>
+      <c r="D8" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15">
       <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" t="s">
         <v>24</v>
       </c>
-      <c r="B9" t="s">
-        <v>25</v>
-      </c>
       <c r="C9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>7</v>
+        <v>22</v>
+      </c>
+      <c r="D9" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15">
       <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
         <v>27</v>
       </c>
-      <c r="B10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>7</v>
+      <c r="D10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15">
       <c r="A11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
         <v>30</v>
       </c>
-      <c r="B11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>18</v>
+      <c r="D11" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15">
       <c r="A12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>7</v>
+      <c r="D12" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15">
       <c r="A13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>36</v>
-      </c>
       <c r="C13" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15">
       <c r="A14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" t="s">
         <v>37</v>
       </c>
-      <c r="B14" t="s">
-        <v>38</v>
-      </c>
       <c r="C14" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15">
       <c r="A15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" t="s">
         <v>39</v>
       </c>
-      <c r="B15" t="s">
-        <v>40</v>
-      </c>
       <c r="C15" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="3" t="s">
         <v>18</v>
+      </c>
+      <c r="D15" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15">
       <c r="A16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" t="s">
         <v>41</v>
       </c>
-      <c r="B16" t="s">
-        <v>28</v>
-      </c>
       <c r="C16" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="15">
+        <v>18</v>
+      </c>
+      <c r="D16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15">
       <c r="A17" t="s">
         <v>42</v>
       </c>
       <c r="B17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15">
+      <c r="A18" t="s">
         <v>43</v>
       </c>
-      <c r="C17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D17" s="3" t="s">
+      <c r="B18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15">
+      <c r="A19" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" ht="15">
-      <c r="A18" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18" t="s">
-        <v>16</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="15">
-      <c r="A19" t="s">
-        <v>46</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="D19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15">
+      <c r="A20" t="s">
         <v>47</v>
       </c>
-      <c r="C19" t="s">
+      <c r="B20" t="s">
         <v>48</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="15">
-      <c r="A20" t="s">
+      <c r="C20" t="s">
         <v>49</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="D20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15">
+      <c r="A21" t="s">
         <v>50</v>
       </c>
-      <c r="C20" t="s">
-        <v>48</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="15">
-      <c r="A21" t="s">
+      <c r="B21" t="s">
         <v>51</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15">
+      <c r="A22" t="s">
         <v>52</v>
       </c>
-      <c r="C21" t="s">
+      <c r="B22" t="s">
         <v>53</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="15">
-      <c r="A22" t="s">
+      <c r="C22" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15">
+      <c r="A23" t="s">
         <v>54</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B23" t="s">
         <v>55</v>
       </c>
-      <c r="C22" t="s">
-        <v>16</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="15">
-      <c r="A23" t="s">
+      <c r="C23" t="s">
         <v>56</v>
       </c>
-      <c r="B23" t="s">
-        <v>25</v>
-      </c>
-      <c r="C23" t="s">
-        <v>26</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="15">
+      <c r="D23" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15">
       <c r="A24" t="s">
         <v>57</v>
       </c>
@@ -1217,614 +1205,650 @@
         <v>58</v>
       </c>
       <c r="C24" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15">
+      <c r="A25" t="s">
         <v>59</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="15">
-      <c r="A25" t="s">
+      <c r="B25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" t="s">
+        <v>27</v>
+      </c>
+      <c r="D25" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15">
+      <c r="A26" t="s">
         <v>60</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B26" t="s">
         <v>61</v>
       </c>
-      <c r="C25" t="s">
-        <v>59</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="15">
-      <c r="A26" t="s">
+      <c r="C26" t="s">
         <v>62</v>
       </c>
-      <c r="B26" t="s">
+      <c r="D26" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="15">
+      <c r="A27" t="s">
         <v>63</v>
       </c>
-      <c r="C26" t="s">
-        <v>59</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="15">
-      <c r="A27" t="s">
+      <c r="B27" t="s">
         <v>64</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
+        <v>62</v>
+      </c>
+      <c r="D27" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15">
+      <c r="A28" t="s">
         <v>65</v>
       </c>
-      <c r="C27" t="s">
+      <c r="B28" t="s">
         <v>66</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="15">
-      <c r="A28" t="s">
+      <c r="C28" t="s">
+        <v>62</v>
+      </c>
+      <c r="D28" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="15">
+      <c r="A29" t="s">
         <v>67</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B29" t="s">
         <v>68</v>
       </c>
-      <c r="C28" t="s">
-        <v>59</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="15">
-      <c r="A29" t="s">
+      <c r="C29" t="s">
         <v>69</v>
       </c>
-      <c r="B29" t="s">
-        <v>28</v>
-      </c>
-      <c r="C29" t="s">
-        <v>29</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="15">
+      <c r="D29" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="15">
       <c r="A30" t="s">
         <v>70</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" t="s">
+        <v>71</v>
+      </c>
+      <c r="C30" t="s">
+        <v>62</v>
+      </c>
+      <c r="D30" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="15">
+      <c r="A31" t="s">
+        <v>72</v>
+      </c>
+      <c r="B31" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" t="s">
+        <v>30</v>
+      </c>
+      <c r="D31" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="15">
+      <c r="A32" t="s">
+        <v>73</v>
+      </c>
+      <c r="B32" t="s">
         <v>5</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C32" t="s">
         <v>6</v>
       </c>
-      <c r="D30" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="15">
-      <c r="A31" t="s">
-        <v>71</v>
-      </c>
-      <c r="B31" t="s">
-        <v>72</v>
-      </c>
-      <c r="C31" t="s">
-        <v>73</v>
-      </c>
-      <c r="D31" s="3" t="s">
+      <c r="D32" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="15">
+      <c r="A33" t="s">
+        <v>74</v>
+      </c>
+      <c r="B33" t="s">
+        <v>75</v>
+      </c>
+      <c r="C33" t="s">
+        <v>76</v>
+      </c>
+      <c r="D33" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="15">
+      <c r="A34" t="s">
+        <v>77</v>
+      </c>
+      <c r="B34" t="s">
+        <v>26</v>
+      </c>
+      <c r="C34" t="s">
+        <v>27</v>
+      </c>
+      <c r="D34" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="15">
+      <c r="A35" t="s">
+        <v>78</v>
+      </c>
+      <c r="B35" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" t="s">
+        <v>27</v>
+      </c>
+      <c r="D35" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="15">
+      <c r="A36" t="s">
+        <v>79</v>
+      </c>
+      <c r="B36" t="s">
+        <v>80</v>
+      </c>
+      <c r="C36" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" ht="15">
-      <c r="A32" t="s">
-        <v>74</v>
-      </c>
-      <c r="B32" t="s">
-        <v>75</v>
-      </c>
-      <c r="C32" t="s">
-        <v>16</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="15">
-      <c r="A33" t="s">
-        <v>76</v>
-      </c>
-      <c r="B33" t="s">
-        <v>77</v>
-      </c>
-      <c r="C33" t="s">
-        <v>78</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="15">
-      <c r="A34" t="s">
-        <v>79</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C34" t="s">
-        <v>59</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="15">
-      <c r="A35" t="s">
+      <c r="D36" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="15">
+      <c r="A37" t="s">
         <v>81</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B37" t="s">
         <v>82</v>
       </c>
-      <c r="C35" t="s">
-        <v>59</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="15">
-      <c r="A36" t="s">
+      <c r="C37" t="s">
         <v>83</v>
       </c>
-      <c r="B36" t="s">
-        <v>61</v>
-      </c>
-      <c r="C36" t="s">
-        <v>59</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="15">
-      <c r="A37" t="s">
+      <c r="D37" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="15">
+      <c r="A38" t="s">
         <v>84</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B38" t="s">
         <v>85</v>
       </c>
-      <c r="C37" t="s">
-        <v>59</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="15">
-      <c r="A38" t="s">
+      <c r="C38" t="s">
+        <v>62</v>
+      </c>
+      <c r="D38" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="15">
+      <c r="A39" t="s">
         <v>86</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B39" t="s">
         <v>87</v>
       </c>
-      <c r="C38" t="s">
-        <v>29</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="15">
-      <c r="A39" t="s">
+      <c r="C39" t="s">
+        <v>62</v>
+      </c>
+      <c r="D39" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="15">
+      <c r="A40" t="s">
         <v>88</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B40" t="s">
+        <v>64</v>
+      </c>
+      <c r="C40" t="s">
+        <v>62</v>
+      </c>
+      <c r="D40" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="15">
+      <c r="A41" t="s">
         <v>89</v>
       </c>
-      <c r="C39" t="s">
-        <v>29</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="15">
-      <c r="A40" t="s">
+      <c r="B41" t="s">
         <v>90</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C41" t="s">
+        <v>62</v>
+      </c>
+      <c r="D41" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="15">
+      <c r="A42" t="s">
         <v>91</v>
       </c>
-      <c r="C40" t="s">
-        <v>29</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" ht="15">
-      <c r="A41" t="s">
+      <c r="B42" t="s">
         <v>92</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C42" t="s">
+        <v>30</v>
+      </c>
+      <c r="D42" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="15">
+      <c r="A43" t="s">
         <v>93</v>
       </c>
-      <c r="C41" t="s">
-        <v>29</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="15">
-      <c r="A42" t="s">
+      <c r="B43" t="s">
         <v>94</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="C43" t="s">
+        <v>30</v>
+      </c>
+      <c r="D43" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="15">
+      <c r="A44" t="s">
         <v>95</v>
       </c>
-      <c r="C42" t="s">
+      <c r="B44" t="s">
         <v>96</v>
       </c>
-      <c r="D42" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" ht="15">
-      <c r="A43" t="s">
+      <c r="C44" t="s">
+        <v>30</v>
+      </c>
+      <c r="D44" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="15">
+      <c r="A45" t="s">
         <v>97</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B45" t="s">
         <v>98</v>
       </c>
-      <c r="C43" t="s">
-        <v>29</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" ht="15">
-      <c r="A44" t="s">
+      <c r="C45" t="s">
+        <v>30</v>
+      </c>
+      <c r="D45" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="15">
+      <c r="A46" t="s">
         <v>99</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B46" t="s">
         <v>100</v>
       </c>
-      <c r="C44" t="s">
-        <v>26</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" ht="15">
-      <c r="A45" t="s">
+      <c r="C46" t="s">
         <v>101</v>
       </c>
-      <c r="B45" t="s">
-        <v>25</v>
-      </c>
-      <c r="C45" t="s">
-        <v>26</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="15">
-      <c r="A46" t="s">
+      <c r="D46" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="15">
+      <c r="A47" t="s">
         <v>102</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B47" t="s">
         <v>103</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C47" t="s">
+        <v>30</v>
+      </c>
+      <c r="D47" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="15">
+      <c r="A48" t="s">
         <v>104</v>
       </c>
-      <c r="D46" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" ht="15">
-      <c r="A47" t="s">
+      <c r="B48" t="s">
         <v>105</v>
       </c>
-      <c r="B47" t="s">
-        <v>106</v>
-      </c>
-      <c r="C47" t="s">
-        <v>16</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" ht="15">
-      <c r="A48" t="s">
-        <v>107</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>108</v>
-      </c>
       <c r="C48" t="s">
-        <v>26</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>7</v>
+        <v>27</v>
+      </c>
+      <c r="D48" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="15">
       <c r="A49" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B49" t="s">
-        <v>110</v>
+        <v>26</v>
       </c>
       <c r="C49" t="s">
-        <v>111</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
+      </c>
+      <c r="D49" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="15">
       <c r="A50" t="s">
-        <v>112</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>113</v>
+        <v>107</v>
+      </c>
+      <c r="B50" t="s">
+        <v>108</v>
       </c>
       <c r="C50" t="s">
-        <v>48</v>
-      </c>
-      <c r="D50" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D50" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="15">
       <c r="A51" t="s">
-        <v>114</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>115</v>
+        <v>110</v>
+      </c>
+      <c r="B51" t="s">
+        <v>111</v>
       </c>
       <c r="C51" t="s">
-        <v>48</v>
-      </c>
-      <c r="D51" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D51" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="15">
       <c r="A52" t="s">
-        <v>116</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>117</v>
+        <v>112</v>
+      </c>
+      <c r="B52" t="s">
+        <v>113</v>
       </c>
       <c r="C52" t="s">
-        <v>16</v>
-      </c>
-      <c r="D52" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D52" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="15">
       <c r="A53" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B53" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C53" t="s">
-        <v>26</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>18</v>
+        <v>116</v>
+      </c>
+      <c r="D53" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="15">
       <c r="A54" t="s">
+        <v>117</v>
+      </c>
+      <c r="B54" t="s">
         <v>118</v>
       </c>
-      <c r="B54" t="s">
-        <v>119</v>
-      </c>
       <c r="C54" t="s">
-        <v>26</v>
-      </c>
-      <c r="D54" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D54" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="15">
       <c r="A55" t="s">
+        <v>119</v>
+      </c>
+      <c r="B55" t="s">
         <v>120</v>
       </c>
-      <c r="B55" s="4" t="s">
-        <v>121</v>
-      </c>
       <c r="C55" t="s">
-        <v>48</v>
-      </c>
-      <c r="D55" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D55" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="15">
       <c r="A56" t="s">
+        <v>121</v>
+      </c>
+      <c r="B56" t="s">
         <v>122</v>
       </c>
-      <c r="B56" t="s">
-        <v>123</v>
-      </c>
       <c r="C56" t="s">
-        <v>59</v>
-      </c>
-      <c r="D56" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D56" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="15">
       <c r="A57" t="s">
+        <v>123</v>
+      </c>
+      <c r="B57" t="s">
         <v>124</v>
       </c>
-      <c r="B57" s="4" t="s">
-        <v>125</v>
-      </c>
       <c r="C57" t="s">
-        <v>48</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>7</v>
+        <v>27</v>
+      </c>
+      <c r="D57" t="s">
+        <v>13</v>
       </c>
       <c r="E57" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="15">
       <c r="A58" t="s">
+        <v>125</v>
+      </c>
+      <c r="B58" t="s">
         <v>126</v>
       </c>
-      <c r="B58" s="4" t="s">
-        <v>127</v>
-      </c>
       <c r="C58" t="s">
-        <v>48</v>
-      </c>
-      <c r="D58" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D58" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="15">
       <c r="A59" t="s">
+        <v>127</v>
+      </c>
+      <c r="B59" t="s">
         <v>128</v>
       </c>
-      <c r="B59" t="s">
-        <v>129</v>
-      </c>
       <c r="C59" t="s">
-        <v>130</v>
+        <v>62</v>
       </c>
       <c r="D59" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="15">
       <c r="A60" t="s">
-        <v>131</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
+      </c>
+      <c r="B60" t="s">
+        <v>130</v>
       </c>
       <c r="C60" t="s">
-        <v>48</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>7</v>
+        <v>49</v>
+      </c>
+      <c r="D60" t="s">
+        <v>7</v>
+      </c>
+      <c r="E60" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="15">
       <c r="A61" t="s">
-        <v>133</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>134</v>
+        <v>131</v>
+      </c>
+      <c r="B61" t="s">
+        <v>132</v>
       </c>
       <c r="C61" t="s">
-        <v>48</v>
-      </c>
-      <c r="D61" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D61" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="15">
       <c r="A62" t="s">
+        <v>133</v>
+      </c>
+      <c r="B62" t="s">
+        <v>134</v>
+      </c>
+      <c r="C62" t="s">
         <v>135</v>
       </c>
-      <c r="B62" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="C62" t="s">
-        <v>16</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>7</v>
+      <c r="D62" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="15">
       <c r="A63" t="s">
+        <v>136</v>
+      </c>
+      <c r="B63" t="s">
         <v>137</v>
       </c>
-      <c r="B63" s="4" t="s">
-        <v>138</v>
-      </c>
       <c r="C63" t="s">
-        <v>16</v>
-      </c>
-      <c r="D63" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D63" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="15">
       <c r="A64" t="s">
+        <v>138</v>
+      </c>
+      <c r="B64" t="s">
         <v>139</v>
       </c>
-      <c r="B64" t="s">
-        <v>140</v>
-      </c>
       <c r="C64" t="s">
-        <v>78</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>18</v>
+        <v>49</v>
+      </c>
+      <c r="D64" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="15">
       <c r="A65" t="s">
+        <v>140</v>
+      </c>
+      <c r="B65" t="s">
         <v>141</v>
       </c>
-      <c r="B65" s="4" t="s">
-        <v>142</v>
-      </c>
       <c r="C65" t="s">
-        <v>29</v>
-      </c>
-      <c r="D65" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D65" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="15">
       <c r="A66" t="s">
+        <v>142</v>
+      </c>
+      <c r="B66" t="s">
         <v>143</v>
       </c>
-      <c r="B66" s="4" t="s">
+      <c r="C66" t="s">
+        <v>18</v>
+      </c>
+      <c r="D66" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="15">
+      <c r="A67" t="s">
         <v>144</v>
       </c>
-      <c r="C66" t="s">
+      <c r="B67" t="s">
+        <v>145</v>
+      </c>
+      <c r="C67" t="s">
+        <v>83</v>
+      </c>
+      <c r="D67" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="15">
+      <c r="A68" t="s">
+        <v>146</v>
+      </c>
+      <c r="B68" t="s">
+        <v>147</v>
+      </c>
+      <c r="C68" t="s">
         <v>6</v>
       </c>
-      <c r="D66" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" ht="15"/>
-    <row r="69" spans="1:4" ht="15"/>
+      <c r="D68" t="s">
+        <v>7</v>
+      </c>
+    </row>
     <row r="70" spans="1:4" ht="15"/>
     <row r="71" spans="1:4" ht="15"/>
+    <row r="72" spans="1:4" ht="15"/>
+    <row r="73" spans="1:4" ht="15"/>
+    <row r="74" spans="1:4" ht="15"/>
+    <row r="75" spans="1:4" ht="15"/>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H66">
-    <sortCondition ref="A2:A66"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H68">
+    <sortCondition ref="A2:A68"/>
   </sortState>
+  <hyperlinks>
+    <hyperlink ref="A4" r:id="rId1" xr:uid="{9C9D4773-DBCF-4009-B4B9-68BFDE689EF3}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/SandBox/maps/Collaborators.xlsx
+++ b/SandBox/maps/Collaborators.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25803"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="288" documentId="11_2783B361715DD81B2B2E30CD8B5EBE776678445D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6873FBE2-AAD3-439F-BEA1-6A20828423E9}"/>
+  <xr:revisionPtr revIDLastSave="369" documentId="11_2783B361715DD81B2B2E30CD8B5EBE776678445D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE47D341-46DA-4BEB-9E8C-07E2EEBA3522}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="175">
   <si>
     <t>Institution</t>
   </si>
@@ -45,6 +45,30 @@
     <t>Who</t>
   </si>
   <si>
+    <t>Abo Adakemi</t>
+  </si>
+  <si>
+    <t>Turku</t>
+  </si>
+  <si>
+    <t>Finland</t>
+  </si>
+  <si>
+    <t>Ray Ryan</t>
+  </si>
+  <si>
+    <t>Atlantic Technological University</t>
+  </si>
+  <si>
+    <t>Galway</t>
+  </si>
+  <si>
+    <t>Ireland</t>
+  </si>
+  <si>
+    <t>John Hinde</t>
+  </si>
+  <si>
     <t>Capital Medical University</t>
   </si>
   <si>
@@ -102,6 +126,15 @@
     <t>India</t>
   </si>
   <si>
+    <t>CSIR0</t>
+  </si>
+  <si>
+    <t>Brisbane</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
     <t>DIT University</t>
   </si>
   <si>
@@ -114,9 +147,6 @@
     <t>Dublin</t>
   </si>
   <si>
-    <t>Ireland</t>
-  </si>
-  <si>
     <t>Ecole Normale Superieure</t>
   </si>
   <si>
@@ -126,6 +156,15 @@
     <t>France</t>
   </si>
   <si>
+    <t>ESALQ/USP</t>
+  </si>
+  <si>
+    <t>Piracicaba</t>
+  </si>
+  <si>
+    <t>Brazil</t>
+  </si>
+  <si>
     <t>FernUniversitat in Hagen</t>
   </si>
   <si>
@@ -144,16 +183,13 @@
     <t>Galway University Hospital</t>
   </si>
   <si>
-    <t>Galway</t>
-  </si>
-  <si>
     <t>Harvard Medical School</t>
   </si>
   <si>
     <t>Boston</t>
   </si>
   <si>
-    <t>Holy Name’s University</t>
+    <t>Holy Names University</t>
   </si>
   <si>
     <t>Oakland</t>
@@ -189,6 +225,15 @@
     <t>London</t>
   </si>
   <si>
+    <t>Massachusetts Institute of Technology</t>
+  </si>
+  <si>
+    <t>Cambridge</t>
+  </si>
+  <si>
+    <t>Harold Berjamin</t>
+  </si>
+  <si>
     <t>Maynooth University</t>
   </si>
   <si>
@@ -234,6 +279,15 @@
     <t>Turin</t>
   </si>
   <si>
+    <t>Prince of Songkla University</t>
+  </si>
+  <si>
+    <t>Hat Yai</t>
+  </si>
+  <si>
+    <t>Thailand</t>
+  </si>
+  <si>
     <t>Russian State Open Technical University of Railway Transport</t>
   </si>
   <si>
@@ -252,6 +306,12 @@
     <t>Sorbonne Université</t>
   </si>
   <si>
+    <t>Technical University of Dublin</t>
+  </si>
+  <si>
+    <t>Trinity College Dublin</t>
+  </si>
+  <si>
     <t>Tsinghua University</t>
   </si>
   <si>
@@ -264,12 +324,6 @@
     <t>Austria</t>
   </si>
   <si>
-    <t>Technical University of Dublin</t>
-  </si>
-  <si>
-    <t>Trinity College Dublin</t>
-  </si>
-  <si>
     <t>Tufts Univerity</t>
   </si>
   <si>
@@ -285,6 +339,21 @@
     <t>Spain</t>
   </si>
   <si>
+    <t>Universidad Torcuato di Tella</t>
+  </si>
+  <si>
+    <t>Buenos Aires</t>
+  </si>
+  <si>
+    <t>Argentina</t>
+  </si>
+  <si>
+    <t>Universidade Federal do Rio de Janeiro</t>
+  </si>
+  <si>
+    <t>Rio de Janeiro</t>
+  </si>
+  <si>
     <t>Università degli studi di Perugia</t>
   </si>
   <si>
@@ -384,6 +453,12 @@
     <t>Cyprus</t>
   </si>
   <si>
+    <t>University of Durham</t>
+  </si>
+  <si>
+    <t>Durham</t>
+  </si>
+  <si>
     <t>University of East Anglia</t>
   </si>
   <si>
@@ -412,6 +487,12 @@
   </si>
   <si>
     <t>Manchester</t>
+  </si>
+  <si>
+    <t>University of Melbourne</t>
+  </si>
+  <si>
+    <t>Melbourne</t>
   </si>
   <si>
     <t>University of Modena and Reggio Emilia</t>
@@ -481,7 +562,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -499,6 +580,11 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="Cambria"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Cambria"/>
       <charset val="1"/>
@@ -539,11 +625,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -859,13 +951,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="36.42578125" customWidth="1"/>
     <col min="2" max="2" width="13.28515625" customWidth="1"/>
     <col min="3" max="3" width="14.5703125" customWidth="1"/>
-    <col min="4" max="4" width="14" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -886,19 +978,22 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
     </row>
-    <row r="2" spans="1:8" ht="15">
-      <c r="A2" t="s">
+    <row r="2" spans="1:8" s="4" customFormat="1" ht="15">
+      <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
     </row>
     <row r="3" spans="1:8" ht="15">
       <c r="A3" t="s">
@@ -919,590 +1014,593 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15">
       <c r="A12" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D12" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C13" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D13" t="s">
-        <v>7</v>
+        <v>15</v>
+      </c>
+      <c r="E13" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="D14" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15">
       <c r="A15" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C15" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="D15" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15">
       <c r="A16" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15">
+      <c r="A17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15">
+      <c r="A18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15">
+      <c r="A19" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15">
+      <c r="A20" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15">
+      <c r="A21" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" t="s">
         <v>40</v>
       </c>
-      <c r="B16" t="s">
-        <v>41</v>
-      </c>
-      <c r="C16" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="15">
-      <c r="A17" t="s">
-        <v>42</v>
-      </c>
-      <c r="B17" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="D21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="15">
+      <c r="A22" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" t="s">
         <v>30</v>
       </c>
-      <c r="D17" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="15">
-      <c r="A18" t="s">
-        <v>43</v>
-      </c>
-      <c r="B18" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="15">
-      <c r="A19" t="s">
-        <v>45</v>
-      </c>
-      <c r="B19" t="s">
-        <v>46</v>
-      </c>
-      <c r="C19" t="s">
-        <v>18</v>
-      </c>
-      <c r="D19" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="15">
-      <c r="A20" t="s">
-        <v>47</v>
-      </c>
-      <c r="B20" t="s">
-        <v>48</v>
-      </c>
-      <c r="C20" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="15">
-      <c r="A21" t="s">
-        <v>50</v>
-      </c>
-      <c r="B21" t="s">
-        <v>51</v>
-      </c>
-      <c r="C21" t="s">
-        <v>49</v>
-      </c>
-      <c r="D21" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="15">
-      <c r="A22" t="s">
-        <v>52</v>
-      </c>
-      <c r="B22" t="s">
-        <v>53</v>
-      </c>
-      <c r="C22" t="s">
-        <v>27</v>
-      </c>
       <c r="D22" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="15">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="15">
       <c r="A23" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B23" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C23" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="D23" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="15">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="15">
       <c r="A24" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B24" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C24" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="D24" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="15">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="15">
       <c r="A25" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B25" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" t="s">
+        <v>61</v>
+      </c>
+      <c r="D25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="15">
+      <c r="A26" t="s">
+        <v>64</v>
+      </c>
+      <c r="B26" t="s">
+        <v>65</v>
+      </c>
+      <c r="C26" t="s">
         <v>26</v>
       </c>
-      <c r="C25" t="s">
-        <v>27</v>
-      </c>
-      <c r="D25" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="15">
-      <c r="A26" t="s">
-        <v>60</v>
-      </c>
-      <c r="B26" t="s">
-        <v>61</v>
-      </c>
-      <c r="C26" t="s">
-        <v>62</v>
-      </c>
       <c r="D26" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="15">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="15">
       <c r="A27" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B27" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C27" t="s">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="D27" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="15">
+        <v>21</v>
+      </c>
+      <c r="E27" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="15">
       <c r="A28" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B28" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C28" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="D28" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="15">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="15">
       <c r="A29" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B29" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C29" t="s">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="D29" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="15">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="15">
       <c r="A30" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B30" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="C30" t="s">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="D30" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="15">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="15">
       <c r="A31" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B31" t="s">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="C31" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="D31" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="15">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="15">
       <c r="A32" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B32" t="s">
-        <v>5</v>
+        <v>79</v>
       </c>
       <c r="C32" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="D32" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="15">
       <c r="A33" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="B33" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C33" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D33" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="15">
       <c r="A34" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B34" t="s">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="C34" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="D34" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="15">
       <c r="A35" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="B35" t="s">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="C35" t="s">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="D35" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="15">
       <c r="A36" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="B36" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C36" t="s">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="D36" t="s">
-        <v>13</v>
-      </c>
-      <c r="E36" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="15">
       <c r="A37" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="B37" t="s">
-        <v>82</v>
+        <v>39</v>
       </c>
       <c r="C37" t="s">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="D37" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="15">
       <c r="A38" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="B38" t="s">
-        <v>85</v>
+        <v>37</v>
       </c>
       <c r="C38" t="s">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="D38" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="15">
       <c r="A39" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B39" t="s">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="C39" t="s">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="D39" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="15">
       <c r="A40" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B40" t="s">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="C40" t="s">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="D40" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="15">
       <c r="A41" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B41" t="s">
-        <v>90</v>
+        <v>13</v>
       </c>
       <c r="C41" t="s">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="D41" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="15">
       <c r="A42" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B42" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C42" t="s">
-        <v>30</v>
+        <v>96</v>
       </c>
       <c r="D42" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="15">
       <c r="A43" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B43" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C43" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D43" t="s">
-        <v>7</v>
+        <v>21</v>
+      </c>
+      <c r="E43" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="15">
       <c r="A44" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B44" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C44" t="s">
-        <v>30</v>
+        <v>101</v>
       </c>
       <c r="D44" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="15">
       <c r="A45" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B45" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C45" t="s">
-        <v>30</v>
+        <v>104</v>
       </c>
       <c r="D45" t="s">
         <v>7</v>
@@ -1510,13 +1608,13 @@
     </row>
     <row r="46" spans="1:5" ht="15">
       <c r="A46" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B46" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C46" t="s">
-        <v>101</v>
+        <v>43</v>
       </c>
       <c r="D46" t="s">
         <v>7</v>
@@ -1524,330 +1622,502 @@
     </row>
     <row r="47" spans="1:5" ht="15">
       <c r="A47" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B47" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C47" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="D47" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="15">
       <c r="A48" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B48" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C48" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="D48" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="E48" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="15">
       <c r="A49" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B49" t="s">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="C49" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="D49" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="15">
       <c r="A50" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B50" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C50" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="D50" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="15">
       <c r="A51" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B51" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C51" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="D51" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="15">
       <c r="A52" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B52" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C52" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="D52" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="15">
       <c r="A53" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B53" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C53" t="s">
-        <v>116</v>
+        <v>40</v>
       </c>
       <c r="D53" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="15">
       <c r="A54" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B54" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C54" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D54" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="15">
       <c r="A55" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B55" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C55" t="s">
-        <v>49</v>
+        <v>124</v>
       </c>
       <c r="D55" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="15">
       <c r="A56" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B56" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C56" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="D56" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="15">
       <c r="A57" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B57" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C57" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="D57" t="s">
-        <v>13</v>
-      </c>
-      <c r="E57" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="15">
       <c r="A58" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B58" t="s">
-        <v>126</v>
+        <v>37</v>
       </c>
       <c r="C58" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="D58" t="s">
+        <v>15</v>
+      </c>
+      <c r="E58" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="15">
       <c r="A59" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B59" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C59" t="s">
-        <v>62</v>
+        <v>132</v>
       </c>
       <c r="D59" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="15">
       <c r="A60" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B60" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C60" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="D60" t="s">
-        <v>7</v>
-      </c>
-      <c r="E60" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="15">
       <c r="A61" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B61" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C61" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="D61" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="15">
       <c r="A62" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B62" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C62" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D62" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="15">
       <c r="A63" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B63" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C63" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D63" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="15">
       <c r="A64" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B64" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C64" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D64" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" ht="15">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="15">
       <c r="A65" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B65" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C65" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="D65" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" ht="15">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="15">
       <c r="A66" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B66" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C66" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D66" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" ht="15">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="15">
       <c r="A67" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B67" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C67" t="s">
-        <v>83</v>
+        <v>10</v>
       </c>
       <c r="D67" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" ht="15">
+        <v>21</v>
+      </c>
+      <c r="E67" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="15">
       <c r="A68" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B68" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C68" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D68" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" ht="15"/>
-    <row r="71" spans="1:4" ht="15"/>
-    <row r="72" spans="1:4" ht="15"/>
-    <row r="73" spans="1:4" ht="15"/>
-    <row r="74" spans="1:4" ht="15"/>
-    <row r="75" spans="1:4" ht="15"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="15">
+      <c r="A69" t="s">
+        <v>150</v>
+      </c>
+      <c r="B69" t="s">
+        <v>151</v>
+      </c>
+      <c r="C69" t="s">
+        <v>61</v>
+      </c>
+      <c r="D69" t="s">
+        <v>15</v>
+      </c>
+      <c r="E69" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="15">
+      <c r="A70" t="s">
+        <v>152</v>
+      </c>
+      <c r="B70" t="s">
+        <v>153</v>
+      </c>
+      <c r="C70" t="s">
+        <v>33</v>
+      </c>
+      <c r="D70" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="15">
+      <c r="A71" t="s">
+        <v>154</v>
+      </c>
+      <c r="B71" t="s">
+        <v>155</v>
+      </c>
+      <c r="C71" t="s">
+        <v>77</v>
+      </c>
+      <c r="D71" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="15">
+      <c r="A72" t="s">
+        <v>156</v>
+      </c>
+      <c r="B72" t="s">
+        <v>157</v>
+      </c>
+      <c r="C72" t="s">
+        <v>61</v>
+      </c>
+      <c r="D72" t="s">
+        <v>15</v>
+      </c>
+      <c r="E72" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="15">
+      <c r="A73" t="s">
+        <v>158</v>
+      </c>
+      <c r="B73" t="s">
+        <v>159</v>
+      </c>
+      <c r="C73" t="s">
+        <v>61</v>
+      </c>
+      <c r="D73" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="15">
+      <c r="A74" t="s">
+        <v>160</v>
+      </c>
+      <c r="B74" t="s">
+        <v>161</v>
+      </c>
+      <c r="C74" t="s">
+        <v>162</v>
+      </c>
+      <c r="D74" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="15">
+      <c r="A75" t="s">
+        <v>163</v>
+      </c>
+      <c r="B75" t="s">
+        <v>164</v>
+      </c>
+      <c r="C75" t="s">
+        <v>61</v>
+      </c>
+      <c r="D75" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="15">
+      <c r="A76" t="s">
+        <v>165</v>
+      </c>
+      <c r="B76" t="s">
+        <v>166</v>
+      </c>
+      <c r="C76" t="s">
+        <v>61</v>
+      </c>
+      <c r="D76" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="15">
+      <c r="A77" t="s">
+        <v>167</v>
+      </c>
+      <c r="B77" t="s">
+        <v>168</v>
+      </c>
+      <c r="C77" t="s">
+        <v>26</v>
+      </c>
+      <c r="D77" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="15">
+      <c r="A78" t="s">
+        <v>169</v>
+      </c>
+      <c r="B78" t="s">
+        <v>170</v>
+      </c>
+      <c r="C78" t="s">
+        <v>26</v>
+      </c>
+      <c r="D78" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="15">
+      <c r="A79" t="s">
+        <v>171</v>
+      </c>
+      <c r="B79" t="s">
+        <v>172</v>
+      </c>
+      <c r="C79" t="s">
+        <v>101</v>
+      </c>
+      <c r="D79" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="15">
+      <c r="A80" t="s">
+        <v>173</v>
+      </c>
+      <c r="B80" t="s">
+        <v>174</v>
+      </c>
+      <c r="C80" t="s">
+        <v>14</v>
+      </c>
+      <c r="D80" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="81" ht="15"/>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H68">
-    <sortCondition ref="A2:A68"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:E80">
+    <sortCondition ref="A3:A80"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="A4" r:id="rId1" xr:uid="{9C9D4773-DBCF-4009-B4B9-68BFDE689EF3}"/>
+    <hyperlink ref="A6" r:id="rId1" xr:uid="{9C9D4773-DBCF-4009-B4B9-68BFDE689EF3}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/SandBox/maps/Collaborators.xlsx
+++ b/SandBox/maps/Collaborators.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25803"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25809"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="369" documentId="11_2783B361715DD81B2B2E30CD8B5EBE776678445D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE47D341-46DA-4BEB-9E8C-07E2EEBA3522}"/>
+  <xr:revisionPtr revIDLastSave="404" documentId="11_2783B361715DD81B2B2E30CD8B5EBE776678445D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6CB3682-9D86-4C40-8459-7F62E3D02414}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="187">
   <si>
     <t>Institution</t>
   </si>
@@ -156,6 +156,18 @@
     <t>France</t>
   </si>
   <si>
+    <t>Einstein College of Medicine</t>
+  </si>
+  <si>
+    <t>New York</t>
+  </si>
+  <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>Cathal Seoighe</t>
+  </si>
+  <si>
     <t>ESALQ/USP</t>
   </si>
   <si>
@@ -306,6 +318,12 @@
     <t>Sorbonne Université</t>
   </si>
   <si>
+    <t>St. Jude Children's Research Hospital</t>
+  </si>
+  <si>
+    <t>Memphis</t>
+  </si>
+  <si>
     <t>Technical University of Dublin</t>
   </si>
   <si>
@@ -444,6 +462,12 @@
     <t>Calgary</t>
   </si>
   <si>
+    <t>University of Cambridge</t>
+  </si>
+  <si>
+    <t>UK</t>
+  </si>
+  <si>
     <t>University of Cyprus</t>
   </si>
   <si>
@@ -465,6 +489,12 @@
     <t>Norwich</t>
   </si>
   <si>
+    <t>University of Edinburgh</t>
+  </si>
+  <si>
+    <t>Edinburgh</t>
+  </si>
+  <si>
     <t>University of Glasgow</t>
   </si>
   <si>
@@ -475,6 +505,12 @@
   </si>
   <si>
     <t>Chicago</t>
+  </si>
+  <si>
+    <t>University of Leeds</t>
+  </si>
+  <si>
+    <t>Leeds</t>
   </si>
   <si>
     <t>University of Limerick</t>
@@ -562,7 +598,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -588,6 +624,11 @@
       <sz val="11"/>
       <name val="Cambria"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -625,7 +666,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -637,6 +678,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -951,7 +993,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H81"/>
+  <dimension ref="A1:H87"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="36.42578125" customWidth="1"/>
@@ -1177,46 +1219,46 @@
         <v>43</v>
       </c>
       <c r="D15" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15">
       <c r="A16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C17" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="D17" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15">
       <c r="A18" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B18" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="C18" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D18" t="s">
         <v>15</v>
@@ -1224,13 +1266,13 @@
     </row>
     <row r="19" spans="1:5" ht="15">
       <c r="A19" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B19" t="s">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="C19" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="D19" t="s">
         <v>15</v>
@@ -1238,69 +1280,69 @@
     </row>
     <row r="20" spans="1:5" ht="15">
       <c r="A20" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B20" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C20" t="s">
         <v>26</v>
       </c>
       <c r="D20" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15">
       <c r="A21" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="C21" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D21" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15">
       <c r="A22" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B22" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="C22" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D22" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15">
       <c r="A23" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B23" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C23" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D23" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15">
       <c r="A24" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B24" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C24" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="D24" t="s">
         <v>15</v>
@@ -1308,13 +1350,13 @@
     </row>
     <row r="25" spans="1:5" ht="15">
       <c r="A25" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C25" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D25" t="s">
         <v>15</v>
@@ -1322,72 +1364,72 @@
     </row>
     <row r="26" spans="1:5" ht="15">
       <c r="A26" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B26" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" t="s">
         <v>65</v>
       </c>
-      <c r="C26" t="s">
-        <v>26</v>
-      </c>
       <c r="D26" t="s">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15">
       <c r="A27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C27" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="D27" t="s">
-        <v>21</v>
-      </c>
-      <c r="E27" t="s">
-        <v>11</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="15">
       <c r="A28" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B28" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C28" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="D28" t="s">
         <v>21</v>
       </c>
+      <c r="E28" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="29" spans="1:5" ht="15">
       <c r="A29" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B29" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="D29" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="15">
       <c r="A30" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B30" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="C30" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="D30" t="s">
         <v>15</v>
@@ -1395,13 +1437,13 @@
     </row>
     <row r="31" spans="1:5" ht="15">
       <c r="A31" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B31" t="s">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="C31" t="s">
-        <v>77</v>
+        <v>10</v>
       </c>
       <c r="D31" t="s">
         <v>15</v>
@@ -1409,13 +1451,13 @@
     </row>
     <row r="32" spans="1:5" ht="15">
       <c r="A32" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B32" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C32" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D32" t="s">
         <v>15</v>
@@ -1423,13 +1465,13 @@
     </row>
     <row r="33" spans="1:5" ht="15">
       <c r="A33" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B33" t="s">
+        <v>83</v>
+      </c>
+      <c r="C33" t="s">
         <v>81</v>
-      </c>
-      <c r="C33" t="s">
-        <v>77</v>
       </c>
       <c r="D33" t="s">
         <v>15</v>
@@ -1437,41 +1479,41 @@
     </row>
     <row r="34" spans="1:5" ht="15">
       <c r="A34" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B34" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C34" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D34" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="15">
       <c r="A35" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B35" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C35" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D35" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="15">
       <c r="A36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B36" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C36" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="D36" t="s">
         <v>15</v>
@@ -1479,13 +1521,13 @@
     </row>
     <row r="37" spans="1:5" ht="15">
       <c r="A37" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B37" t="s">
-        <v>39</v>
+        <v>93</v>
       </c>
       <c r="C37" t="s">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="D37" t="s">
         <v>15</v>
@@ -1493,35 +1535,35 @@
     </row>
     <row r="38" spans="1:5" ht="15">
       <c r="A38" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B38" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C38" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D38" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="15">
       <c r="A39" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B39" t="s">
-        <v>37</v>
+        <v>96</v>
       </c>
       <c r="C39" t="s">
-        <v>10</v>
-      </c>
-      <c r="D39" t="s">
-        <v>21</v>
+        <v>43</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="15">
       <c r="A40" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B40" t="s">
         <v>37</v>
@@ -1530,80 +1572,83 @@
         <v>10</v>
       </c>
       <c r="D40" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="15">
       <c r="A41" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B41" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="C41" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D41" t="s">
-        <v>15</v>
+        <v>21</v>
+      </c>
+      <c r="E41" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="15">
       <c r="A42" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B42" t="s">
-        <v>95</v>
+        <v>37</v>
       </c>
       <c r="C42" t="s">
-        <v>96</v>
+        <v>10</v>
       </c>
       <c r="D42" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="15">
       <c r="A43" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B43" t="s">
-        <v>98</v>
+        <v>13</v>
       </c>
       <c r="C43" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D43" t="s">
-        <v>21</v>
-      </c>
-      <c r="E43" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="15">
       <c r="A44" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B44" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C44" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D44" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="15">
       <c r="A45" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B45" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C45" t="s">
-        <v>104</v>
+        <v>26</v>
       </c>
       <c r="D45" t="s">
-        <v>7</v>
+        <v>21</v>
+      </c>
+      <c r="E45" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="15">
@@ -1614,52 +1659,49 @@
         <v>106</v>
       </c>
       <c r="C46" t="s">
-        <v>43</v>
+        <v>107</v>
       </c>
       <c r="D46" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="15">
       <c r="A47" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B47" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C47" t="s">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="D47" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="15">
       <c r="A48" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B48" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C48" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="D48" t="s">
-        <v>15</v>
-      </c>
-      <c r="E48" t="s">
-        <v>66</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="15">
       <c r="A49" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B49" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="C49" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D49" t="s">
         <v>15</v>
@@ -1667,27 +1709,30 @@
     </row>
     <row r="50" spans="1:5" ht="15">
       <c r="A50" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B50" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C50" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D50" t="s">
         <v>15</v>
+      </c>
+      <c r="E50" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="15">
       <c r="A51" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B51" t="s">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C51" t="s">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="D51" t="s">
         <v>15</v>
@@ -1695,13 +1740,13 @@
     </row>
     <row r="52" spans="1:5" ht="15">
       <c r="A52" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B52" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C52" t="s">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="D52" t="s">
         <v>15</v>
@@ -1709,10 +1754,10 @@
     </row>
     <row r="53" spans="1:5" ht="15">
       <c r="A53" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B53" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C53" t="s">
         <v>40</v>
@@ -1723,10 +1768,10 @@
     </row>
     <row r="54" spans="1:5" ht="15">
       <c r="A54" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B54" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C54" t="s">
         <v>40</v>
@@ -1737,13 +1782,13 @@
     </row>
     <row r="55" spans="1:5" ht="15">
       <c r="A55" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B55" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C55" t="s">
-        <v>124</v>
+        <v>40</v>
       </c>
       <c r="D55" t="s">
         <v>15</v>
@@ -1751,10 +1796,10 @@
     </row>
     <row r="56" spans="1:5" ht="15">
       <c r="A56" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B56" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C56" t="s">
         <v>40</v>
@@ -1765,72 +1810,75 @@
     </row>
     <row r="57" spans="1:5" ht="15">
       <c r="A57" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B57" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C57" t="s">
-        <v>10</v>
+        <v>130</v>
       </c>
       <c r="D57" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="15">
       <c r="A58" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B58" t="s">
-        <v>37</v>
+        <v>132</v>
       </c>
       <c r="C58" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D58" t="s">
         <v>15</v>
-      </c>
-      <c r="E58" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="15">
       <c r="A59" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B59" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C59" t="s">
-        <v>132</v>
+        <v>10</v>
       </c>
       <c r="D59" t="s">
-        <v>15</v>
+        <v>21</v>
+      </c>
+      <c r="E59" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="15">
       <c r="A60" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B60" t="s">
-        <v>134</v>
+        <v>37</v>
       </c>
       <c r="C60" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="D60" t="s">
         <v>15</v>
+      </c>
+      <c r="E60" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="15">
       <c r="A61" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B61" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C61" t="s">
-        <v>10</v>
+        <v>138</v>
       </c>
       <c r="D61" t="s">
         <v>15</v>
@@ -1838,218 +1886,215 @@
     </row>
     <row r="62" spans="1:5" ht="15">
       <c r="A62" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B62" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C62" t="s">
-        <v>139</v>
+        <v>26</v>
       </c>
       <c r="D62" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="15">
       <c r="A63" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B63" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C63" t="s">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="D63" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="15">
       <c r="A64" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B64" t="s">
-        <v>143</v>
+        <v>69</v>
       </c>
       <c r="C64" t="s">
-        <v>61</v>
+        <v>144</v>
       </c>
       <c r="D64" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="15">
       <c r="A65" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B65" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C65" t="s">
-        <v>61</v>
+        <v>147</v>
       </c>
       <c r="D65" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="15">
       <c r="A66" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B66" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C66" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="D66" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="15">
       <c r="A67" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B67" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C67" t="s">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="D67" t="s">
-        <v>21</v>
-      </c>
-      <c r="E67" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="15">
       <c r="A68" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B68" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C68" t="s">
-        <v>10</v>
+        <v>144</v>
       </c>
       <c r="D68" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="15">
       <c r="A69" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B69" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C69" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D69" t="s">
         <v>15</v>
-      </c>
-      <c r="E69" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="15">
       <c r="A70" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B70" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C70" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D70" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="15">
       <c r="A71" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B71" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C71" t="s">
-        <v>77</v>
+        <v>144</v>
       </c>
       <c r="D71" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="15">
       <c r="A72" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B72" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C72" t="s">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="D72" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E72" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="15">
       <c r="A73" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B73" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C73" t="s">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="D73" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="15">
       <c r="A74" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B74" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C74" t="s">
-        <v>162</v>
+        <v>65</v>
       </c>
       <c r="D74" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="E74" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="15">
       <c r="A75" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B75" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C75" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="D75" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="15">
       <c r="A76" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B76" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C76" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="D76" t="s">
         <v>15</v>
@@ -2057,27 +2102,30 @@
     </row>
     <row r="77" spans="1:5" ht="15">
       <c r="A77" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B77" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C77" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="D77" t="s">
         <v>15</v>
+      </c>
+      <c r="E77" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="15">
       <c r="A78" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B78" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C78" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="D78" t="s">
         <v>15</v>
@@ -2085,36 +2133,111 @@
     </row>
     <row r="79" spans="1:5" ht="15">
       <c r="A79" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B79" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C79" t="s">
-        <v>101</v>
+        <v>174</v>
       </c>
       <c r="D79" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="15">
       <c r="A80" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B80" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C80" t="s">
+        <v>65</v>
+      </c>
+      <c r="D80" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="15">
+      <c r="A81" t="s">
+        <v>177</v>
+      </c>
+      <c r="B81" t="s">
+        <v>178</v>
+      </c>
+      <c r="C81" t="s">
+        <v>65</v>
+      </c>
+      <c r="D81" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="15">
+      <c r="A82" t="s">
+        <v>179</v>
+      </c>
+      <c r="B82" t="s">
+        <v>180</v>
+      </c>
+      <c r="C82" t="s">
+        <v>26</v>
+      </c>
+      <c r="D82" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="15">
+      <c r="A83" t="s">
+        <v>181</v>
+      </c>
+      <c r="B83" t="s">
+        <v>182</v>
+      </c>
+      <c r="C83" t="s">
+        <v>26</v>
+      </c>
+      <c r="D83" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="15">
+      <c r="A84" t="s">
+        <v>183</v>
+      </c>
+      <c r="B84" t="s">
+        <v>184</v>
+      </c>
+      <c r="C84" t="s">
+        <v>107</v>
+      </c>
+      <c r="D84" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="15">
+      <c r="A85" t="s">
+        <v>185</v>
+      </c>
+      <c r="B85" t="s">
+        <v>186</v>
+      </c>
+      <c r="C85" t="s">
         <v>14</v>
       </c>
-      <c r="D80" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="81" ht="15"/>
+      <c r="D85" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="15">
+      <c r="D86"/>
+    </row>
+    <row r="87" spans="1:4" ht="15">
+      <c r="D87"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:E80">
-    <sortCondition ref="A3:A80"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:E85">
+    <sortCondition ref="A3:A85"/>
   </sortState>
   <hyperlinks>
     <hyperlink ref="A6" r:id="rId1" xr:uid="{9C9D4773-DBCF-4009-B4B9-68BFDE689EF3}"/>

--- a/SandBox/maps/Collaborators.xlsx
+++ b/SandBox/maps/Collaborators.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25809"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25825"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="404" documentId="11_2783B361715DD81B2B2E30CD8B5EBE776678445D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6CB3682-9D86-4C40-8459-7F62E3D02414}"/>
+  <xr:revisionPtr revIDLastSave="435" documentId="11_2783B361715DD81B2B2E30CD8B5EBE776678445D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D430A311-E04E-4B19-A125-20DD7B9AAB7B}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="199">
   <si>
     <t>Institution</t>
   </si>
@@ -216,6 +216,18 @@
     <t>Tiruchirappalli</t>
   </si>
   <si>
+    <t>IITIS, Polish Academy of Sciences</t>
+  </si>
+  <si>
+    <t>Gliwice</t>
+  </si>
+  <si>
+    <t>Poland</t>
+  </si>
+  <si>
+    <t>Michael Mc Gettrick</t>
+  </si>
+  <si>
     <t>Indiana University–Purdue University</t>
   </si>
   <si>
@@ -261,6 +273,12 @@
     <t>Canada</t>
   </si>
   <si>
+    <t>Nanjing University of Aeronautics and Astronautics</t>
+  </si>
+  <si>
+    <t>Nanjing</t>
+  </si>
+  <si>
     <t>Naval Research Laboratory</t>
   </si>
   <si>
@@ -357,6 +375,12 @@
     <t>Spain</t>
   </si>
   <si>
+    <t>Universidad Rovira i Verguli</t>
+  </si>
+  <si>
+    <t>Tarragona</t>
+  </si>
+  <si>
     <t>Universidad Torcuato di Tella</t>
   </si>
   <si>
@@ -417,6 +441,12 @@
     <t>Tours</t>
   </si>
   <si>
+    <t>Universite Grenoble Alpes</t>
+  </si>
+  <si>
+    <t>Grenoble</t>
+  </si>
+  <si>
     <t>Université Libre de Bruxelles</t>
   </si>
   <si>
@@ -465,34 +495,40 @@
     <t>University of Cambridge</t>
   </si>
   <si>
+    <t>University of Cyprus</t>
+  </si>
+  <si>
+    <t>Nicosia</t>
+  </si>
+  <si>
+    <t>Cyprus</t>
+  </si>
+  <si>
+    <t>University of Durham</t>
+  </si>
+  <si>
+    <t>Durham</t>
+  </si>
+  <si>
+    <t>University of East Anglia</t>
+  </si>
+  <si>
+    <t>Norwich</t>
+  </si>
+  <si>
+    <t>University of Edinburgh</t>
+  </si>
+  <si>
+    <t>Edinburgh</t>
+  </si>
+  <si>
     <t>UK</t>
   </si>
   <si>
-    <t>University of Cyprus</t>
-  </si>
-  <si>
-    <t>Nicosia</t>
-  </si>
-  <si>
-    <t>Cyprus</t>
-  </si>
-  <si>
-    <t>University of Durham</t>
-  </si>
-  <si>
-    <t>Durham</t>
-  </si>
-  <si>
-    <t>University of East Anglia</t>
-  </si>
-  <si>
-    <t>Norwich</t>
-  </si>
-  <si>
-    <t>University of Edinburgh</t>
-  </si>
-  <si>
-    <t>Edinburgh</t>
+    <t>University of Gdansk</t>
+  </si>
+  <si>
+    <t>Gdansk</t>
   </si>
   <si>
     <t>University of Glasgow</t>
@@ -993,7 +1029,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H87"/>
+  <dimension ref="A1:H91"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="36.42578125" customWidth="1"/>
@@ -1033,9 +1069,9 @@
       <c r="D2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="F2"/>
+      <c r="G2"/>
+      <c r="H2"/>
     </row>
     <row r="3" spans="1:8" ht="15">
       <c r="A3" t="s">
@@ -1221,6 +1257,9 @@
       <c r="D15" t="s">
         <v>44</v>
       </c>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
     </row>
     <row r="16" spans="1:8" ht="15">
       <c r="A16" t="s">
@@ -1342,21 +1381,21 @@
         <v>62</v>
       </c>
       <c r="C24" t="s">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="D24" t="s">
-        <v>15</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15">
       <c r="A25" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B25" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C25" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="D25" t="s">
         <v>15</v>
@@ -1364,13 +1403,13 @@
     </row>
     <row r="26" spans="1:5" ht="15">
       <c r="A26" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C26" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D26" t="s">
         <v>15</v>
@@ -1378,86 +1417,86 @@
     </row>
     <row r="27" spans="1:5" ht="15">
       <c r="A27" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B27" t="s">
+        <v>71</v>
+      </c>
+      <c r="C27" t="s">
         <v>69</v>
       </c>
-      <c r="C27" t="s">
-        <v>26</v>
-      </c>
       <c r="D27" t="s">
-        <v>70</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="15">
       <c r="A28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B28" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C28" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="D28" t="s">
-        <v>21</v>
-      </c>
-      <c r="E28" t="s">
-        <v>11</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="15">
       <c r="A29" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B29" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C29" t="s">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="D29" t="s">
         <v>21</v>
       </c>
+      <c r="E29" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="30" spans="1:5" ht="15">
       <c r="A30" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B30" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C30" t="s">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="D30" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="15">
       <c r="A31" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B31" t="s">
-        <v>37</v>
+        <v>81</v>
       </c>
       <c r="C31" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D31" t="s">
-        <v>15</v>
+        <v>64</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="15">
       <c r="A32" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B32" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C32" t="s">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="D32" t="s">
         <v>15</v>
@@ -1465,13 +1504,13 @@
     </row>
     <row r="33" spans="1:5" ht="15">
       <c r="A33" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B33" t="s">
-        <v>83</v>
+        <v>37</v>
       </c>
       <c r="C33" t="s">
-        <v>81</v>
+        <v>10</v>
       </c>
       <c r="D33" t="s">
         <v>15</v>
@@ -1479,13 +1518,13 @@
     </row>
     <row r="34" spans="1:5" ht="15">
       <c r="A34" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B34" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C34" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D34" t="s">
         <v>15</v>
@@ -1493,27 +1532,27 @@
     </row>
     <row r="35" spans="1:5" ht="15">
       <c r="A35" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B35" t="s">
+        <v>89</v>
+      </c>
+      <c r="C35" t="s">
         <v>87</v>
       </c>
-      <c r="C35" t="s">
-        <v>88</v>
-      </c>
       <c r="D35" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="15">
       <c r="A36" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B36" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C36" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D36" t="s">
         <v>15</v>
@@ -1527,21 +1566,21 @@
         <v>93</v>
       </c>
       <c r="C37" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="D37" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="15">
       <c r="A38" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B38" t="s">
-        <v>39</v>
+        <v>96</v>
       </c>
       <c r="C38" t="s">
-        <v>40</v>
+        <v>97</v>
       </c>
       <c r="D38" t="s">
         <v>15</v>
@@ -1549,52 +1588,49 @@
     </row>
     <row r="39" spans="1:5" ht="15">
       <c r="A39" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B39" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C39" t="s">
-        <v>43</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>44</v>
+        <v>87</v>
+      </c>
+      <c r="D39" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="15">
       <c r="A40" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B40" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C40" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D40" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="15">
       <c r="A41" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B41" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="C41" t="s">
-        <v>10</v>
-      </c>
-      <c r="D41" t="s">
-        <v>21</v>
-      </c>
-      <c r="E41" t="s">
+        <v>43</v>
+      </c>
+      <c r="D41" s="5" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="15">
       <c r="A42" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B42" t="s">
         <v>37</v>
@@ -1603,80 +1639,83 @@
         <v>10</v>
       </c>
       <c r="D42" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="15">
       <c r="A43" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B43" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="C43" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D43" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="15">
       <c r="A44" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B44" t="s">
-        <v>101</v>
+        <v>37</v>
       </c>
       <c r="C44" t="s">
-        <v>102</v>
+        <v>10</v>
       </c>
       <c r="D44" t="s">
         <v>21</v>
       </c>
+      <c r="E44" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="45" spans="1:5" ht="15">
       <c r="A45" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B45" t="s">
-        <v>104</v>
+        <v>13</v>
       </c>
       <c r="C45" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D45" t="s">
-        <v>21</v>
-      </c>
-      <c r="E45" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="15">
       <c r="A46" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B46" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C46" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D46" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="15">
       <c r="A47" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B47" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C47" t="s">
-        <v>110</v>
+        <v>26</v>
       </c>
       <c r="D47" t="s">
-        <v>7</v>
+        <v>21</v>
+      </c>
+      <c r="E47" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="15">
@@ -1687,66 +1726,63 @@
         <v>112</v>
       </c>
       <c r="C48" t="s">
-        <v>47</v>
+        <v>113</v>
       </c>
       <c r="D48" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="15">
       <c r="A49" t="s">
+        <v>114</v>
+      </c>
+      <c r="B49" t="s">
+        <v>115</v>
+      </c>
+      <c r="C49" t="s">
         <v>113</v>
       </c>
-      <c r="B49" t="s">
-        <v>114</v>
-      </c>
-      <c r="C49" t="s">
-        <v>81</v>
-      </c>
-      <c r="D49" t="s">
-        <v>15</v>
+      <c r="D49" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="15">
       <c r="A50" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B50" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C50" t="s">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="D50" t="s">
-        <v>15</v>
-      </c>
-      <c r="E50" t="s">
-        <v>70</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="15">
       <c r="A51" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B51" t="s">
-        <v>83</v>
+        <v>120</v>
       </c>
       <c r="C51" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="D51" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="15">
       <c r="A52" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B52" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C52" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D52" t="s">
         <v>15</v>
@@ -1754,27 +1790,30 @@
     </row>
     <row r="53" spans="1:5" ht="15">
       <c r="A53" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B53" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C53" t="s">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="D53" t="s">
         <v>15</v>
+      </c>
+      <c r="E53" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="15">
       <c r="A54" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B54" t="s">
-        <v>123</v>
+        <v>89</v>
       </c>
       <c r="C54" t="s">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="D54" t="s">
         <v>15</v>
@@ -1782,13 +1821,13 @@
     </row>
     <row r="55" spans="1:5" ht="15">
       <c r="A55" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B55" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C55" t="s">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="D55" t="s">
         <v>15</v>
@@ -1796,10 +1835,10 @@
     </row>
     <row r="56" spans="1:5" ht="15">
       <c r="A56" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B56" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C56" t="s">
         <v>40</v>
@@ -1810,13 +1849,13 @@
     </row>
     <row r="57" spans="1:5" ht="15">
       <c r="A57" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B57" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C57" t="s">
-        <v>130</v>
+        <v>40</v>
       </c>
       <c r="D57" t="s">
         <v>15</v>
@@ -1824,10 +1863,10 @@
     </row>
     <row r="58" spans="1:5" ht="15">
       <c r="A58" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B58" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C58" t="s">
         <v>40</v>
@@ -1838,47 +1877,41 @@
     </row>
     <row r="59" spans="1:5" ht="15">
       <c r="A59" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B59" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C59" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D59" t="s">
-        <v>21</v>
-      </c>
-      <c r="E59" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="15">
       <c r="A60" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B60" t="s">
-        <v>37</v>
+        <v>137</v>
       </c>
       <c r="C60" t="s">
-        <v>10</v>
-      </c>
-      <c r="D60" t="s">
-        <v>15</v>
-      </c>
-      <c r="E60" t="s">
-        <v>7</v>
+        <v>40</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="15">
       <c r="A61" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B61" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C61" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D61" t="s">
         <v>15</v>
@@ -1886,13 +1919,13 @@
     </row>
     <row r="62" spans="1:5" ht="15">
       <c r="A62" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B62" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C62" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="D62" t="s">
         <v>15</v>
@@ -1900,89 +1933,98 @@
     </row>
     <row r="63" spans="1:5" ht="15">
       <c r="A63" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B63" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C63" t="s">
         <v>10</v>
       </c>
       <c r="D63" t="s">
-        <v>15</v>
+        <v>21</v>
+      </c>
+      <c r="E63" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="15">
       <c r="A64" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B64" t="s">
+        <v>37</v>
+      </c>
+      <c r="C64" t="s">
+        <v>10</v>
+      </c>
+      <c r="D64" t="s">
+        <v>15</v>
+      </c>
+      <c r="E64" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="15">
+      <c r="A65" t="s">
+        <v>146</v>
+      </c>
+      <c r="B65" t="s">
+        <v>147</v>
+      </c>
+      <c r="C65" t="s">
+        <v>148</v>
+      </c>
+      <c r="D65" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="15">
+      <c r="A66" t="s">
+        <v>149</v>
+      </c>
+      <c r="B66" t="s">
+        <v>150</v>
+      </c>
+      <c r="C66" t="s">
+        <v>26</v>
+      </c>
+      <c r="D66" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="15">
+      <c r="A67" t="s">
+        <v>151</v>
+      </c>
+      <c r="B67" t="s">
+        <v>152</v>
+      </c>
+      <c r="C67" t="s">
+        <v>10</v>
+      </c>
+      <c r="D67" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="15">
+      <c r="A68" t="s">
+        <v>153</v>
+      </c>
+      <c r="B68" t="s">
+        <v>73</v>
+      </c>
+      <c r="C68" t="s">
         <v>69</v>
       </c>
-      <c r="C64" t="s">
-        <v>144</v>
-      </c>
-      <c r="D64" t="s">
+      <c r="D68" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E68" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="15">
-      <c r="A65" t="s">
-        <v>145</v>
-      </c>
-      <c r="B65" t="s">
-        <v>146</v>
-      </c>
-      <c r="C65" t="s">
-        <v>147</v>
-      </c>
-      <c r="D65" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" ht="15">
-      <c r="A66" t="s">
-        <v>148</v>
-      </c>
-      <c r="B66" t="s">
-        <v>149</v>
-      </c>
-      <c r="C66" t="s">
-        <v>65</v>
-      </c>
-      <c r="D66" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" ht="15">
-      <c r="A67" t="s">
-        <v>150</v>
-      </c>
-      <c r="B67" t="s">
-        <v>151</v>
-      </c>
-      <c r="C67" t="s">
-        <v>65</v>
-      </c>
-      <c r="D67" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" ht="15">
-      <c r="A68" t="s">
-        <v>152</v>
-      </c>
-      <c r="B68" t="s">
-        <v>153</v>
-      </c>
-      <c r="C68" t="s">
-        <v>144</v>
-      </c>
-      <c r="D68" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" ht="15">
+    <row r="69" spans="1:6" ht="15">
       <c r="A69" t="s">
         <v>154</v>
       </c>
@@ -1990,254 +2032,319 @@
         <v>155</v>
       </c>
       <c r="C69" t="s">
-        <v>65</v>
+        <v>156</v>
       </c>
       <c r="D69" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" ht="15">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="15">
       <c r="A70" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B70" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C70" t="s">
+        <v>69</v>
+      </c>
+      <c r="D70" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="15">
+      <c r="A71" t="s">
+        <v>159</v>
+      </c>
+      <c r="B71" t="s">
+        <v>160</v>
+      </c>
+      <c r="C71" t="s">
+        <v>69</v>
+      </c>
+      <c r="D71" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="15">
+      <c r="A72" t="s">
+        <v>161</v>
+      </c>
+      <c r="B72" t="s">
+        <v>162</v>
+      </c>
+      <c r="C72" t="s">
+        <v>163</v>
+      </c>
+      <c r="D72" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="15">
+      <c r="A73" t="s">
+        <v>164</v>
+      </c>
+      <c r="B73" t="s">
+        <v>165</v>
+      </c>
+      <c r="C73" t="s">
+        <v>63</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="15">
+      <c r="A74" t="s">
+        <v>166</v>
+      </c>
+      <c r="B74" t="s">
+        <v>167</v>
+      </c>
+      <c r="C74" t="s">
+        <v>69</v>
+      </c>
+      <c r="D74" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="15">
+      <c r="A75" t="s">
+        <v>168</v>
+      </c>
+      <c r="B75" t="s">
+        <v>169</v>
+      </c>
+      <c r="C75" t="s">
         <v>26</v>
       </c>
-      <c r="D70" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" ht="15">
-      <c r="A71" t="s">
-        <v>158</v>
-      </c>
-      <c r="B71" t="s">
-        <v>159</v>
-      </c>
-      <c r="C71" t="s">
-        <v>144</v>
-      </c>
-      <c r="D71" t="s">
+      <c r="D75" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="15">
+      <c r="A76" t="s">
+        <v>170</v>
+      </c>
+      <c r="B76" t="s">
+        <v>171</v>
+      </c>
+      <c r="C76" t="s">
+        <v>163</v>
+      </c>
+      <c r="D76" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="15">
-      <c r="A72" t="s">
-        <v>160</v>
-      </c>
-      <c r="B72" t="s">
-        <v>161</v>
-      </c>
-      <c r="C72" t="s">
+    <row r="77" spans="1:6" ht="15">
+      <c r="A77" t="s">
+        <v>172</v>
+      </c>
+      <c r="B77" t="s">
+        <v>173</v>
+      </c>
+      <c r="C77" t="s">
         <v>10</v>
       </c>
-      <c r="D72" t="s">
+    </row>
+    <row r="78" spans="1:6" ht="15">
+      <c r="A78" t="s">
+        <v>172</v>
+      </c>
+      <c r="B78" t="s">
+        <v>173</v>
+      </c>
+      <c r="C78" t="s">
+        <v>10</v>
+      </c>
+      <c r="D78" t="s">
         <v>21</v>
       </c>
-      <c r="E72" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" ht="15">
-      <c r="A73" t="s">
-        <v>160</v>
-      </c>
-      <c r="B73" t="s">
-        <v>161</v>
-      </c>
-      <c r="C73" t="s">
-        <v>10</v>
-      </c>
-      <c r="D73" t="s">
+      <c r="E78" t="s">
+        <v>15</v>
+      </c>
+      <c r="F78" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="15">
-      <c r="A74" t="s">
-        <v>162</v>
-      </c>
-      <c r="B74" t="s">
-        <v>163</v>
-      </c>
-      <c r="C74" t="s">
-        <v>65</v>
-      </c>
-      <c r="D74" t="s">
-        <v>15</v>
-      </c>
-      <c r="E74" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" ht="15">
-      <c r="A75" t="s">
-        <v>164</v>
-      </c>
-      <c r="B75" t="s">
-        <v>165</v>
-      </c>
-      <c r="C75" t="s">
+    <row r="79" spans="1:6" ht="15">
+      <c r="A79" t="s">
+        <v>174</v>
+      </c>
+      <c r="B79" t="s">
+        <v>175</v>
+      </c>
+      <c r="C79" t="s">
+        <v>69</v>
+      </c>
+      <c r="D79" t="s">
+        <v>15</v>
+      </c>
+      <c r="E79" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="15">
+      <c r="A80" t="s">
+        <v>176</v>
+      </c>
+      <c r="B80" t="s">
+        <v>177</v>
+      </c>
+      <c r="C80" t="s">
         <v>33</v>
       </c>
-      <c r="D75" t="s">
+      <c r="D80" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="15">
-      <c r="A76" t="s">
-        <v>166</v>
-      </c>
-      <c r="B76" t="s">
-        <v>167</v>
-      </c>
-      <c r="C76" t="s">
-        <v>81</v>
-      </c>
-      <c r="D76" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" ht="15">
-      <c r="A77" t="s">
-        <v>168</v>
-      </c>
-      <c r="B77" t="s">
-        <v>169</v>
-      </c>
-      <c r="C77" t="s">
-        <v>65</v>
-      </c>
-      <c r="D77" t="s">
-        <v>15</v>
-      </c>
-      <c r="E77" t="s">
+    <row r="81" spans="1:5" ht="15">
+      <c r="A81" t="s">
+        <v>178</v>
+      </c>
+      <c r="B81" t="s">
+        <v>179</v>
+      </c>
+      <c r="C81" t="s">
+        <v>87</v>
+      </c>
+      <c r="D81" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="15">
+      <c r="A82" t="s">
+        <v>180</v>
+      </c>
+      <c r="B82" t="s">
+        <v>181</v>
+      </c>
+      <c r="C82" t="s">
+        <v>69</v>
+      </c>
+      <c r="D82" t="s">
+        <v>15</v>
+      </c>
+      <c r="E82" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="15">
-      <c r="A78" t="s">
-        <v>170</v>
-      </c>
-      <c r="B78" t="s">
-        <v>171</v>
-      </c>
-      <c r="C78" t="s">
-        <v>65</v>
-      </c>
-      <c r="D78" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" ht="15">
-      <c r="A79" t="s">
-        <v>172</v>
-      </c>
-      <c r="B79" t="s">
-        <v>173</v>
-      </c>
-      <c r="C79" t="s">
-        <v>174</v>
-      </c>
-      <c r="D79" t="s">
+    <row r="83" spans="1:5" ht="15">
+      <c r="A83" t="s">
+        <v>182</v>
+      </c>
+      <c r="B83" t="s">
+        <v>183</v>
+      </c>
+      <c r="C83" t="s">
+        <v>69</v>
+      </c>
+      <c r="D83" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="15">
+      <c r="A84" t="s">
+        <v>184</v>
+      </c>
+      <c r="B84" t="s">
+        <v>185</v>
+      </c>
+      <c r="C84" t="s">
+        <v>186</v>
+      </c>
+      <c r="D84" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="15">
-      <c r="A80" t="s">
-        <v>175</v>
-      </c>
-      <c r="B80" t="s">
-        <v>176</v>
-      </c>
-      <c r="C80" t="s">
-        <v>65</v>
-      </c>
-      <c r="D80" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" ht="15">
-      <c r="A81" t="s">
-        <v>177</v>
-      </c>
-      <c r="B81" t="s">
-        <v>178</v>
-      </c>
-      <c r="C81" t="s">
-        <v>65</v>
-      </c>
-      <c r="D81" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" ht="15">
-      <c r="A82" t="s">
-        <v>179</v>
-      </c>
-      <c r="B82" t="s">
-        <v>180</v>
-      </c>
-      <c r="C82" t="s">
+    <row r="85" spans="1:5" ht="15">
+      <c r="A85" t="s">
+        <v>187</v>
+      </c>
+      <c r="B85" t="s">
+        <v>188</v>
+      </c>
+      <c r="C85" t="s">
+        <v>69</v>
+      </c>
+      <c r="D85" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="15">
+      <c r="A86" t="s">
+        <v>189</v>
+      </c>
+      <c r="B86" t="s">
+        <v>190</v>
+      </c>
+      <c r="C86" t="s">
+        <v>69</v>
+      </c>
+      <c r="D86" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" ht="15">
+      <c r="A87" t="s">
+        <v>191</v>
+      </c>
+      <c r="B87" t="s">
+        <v>192</v>
+      </c>
+      <c r="C87" t="s">
         <v>26</v>
       </c>
-      <c r="D82" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" ht="15">
-      <c r="A83" t="s">
-        <v>181</v>
-      </c>
-      <c r="B83" t="s">
-        <v>182</v>
-      </c>
-      <c r="C83" t="s">
+      <c r="D87" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="15">
+      <c r="A88" t="s">
+        <v>193</v>
+      </c>
+      <c r="B88" t="s">
+        <v>194</v>
+      </c>
+      <c r="C88" t="s">
         <v>26</v>
       </c>
-      <c r="D83" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" ht="15">
-      <c r="A84" t="s">
-        <v>183</v>
-      </c>
-      <c r="B84" t="s">
-        <v>184</v>
-      </c>
-      <c r="C84" t="s">
-        <v>107</v>
-      </c>
-      <c r="D84" t="s">
+      <c r="D88" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="15">
+      <c r="A89" t="s">
+        <v>195</v>
+      </c>
+      <c r="B89" t="s">
+        <v>196</v>
+      </c>
+      <c r="C89" t="s">
+        <v>113</v>
+      </c>
+      <c r="D89" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="15">
-      <c r="A85" t="s">
-        <v>185</v>
-      </c>
-      <c r="B85" t="s">
-        <v>186</v>
-      </c>
-      <c r="C85" t="s">
+    <row r="90" spans="1:5" ht="15">
+      <c r="A90" t="s">
+        <v>197</v>
+      </c>
+      <c r="B90" t="s">
+        <v>198</v>
+      </c>
+      <c r="C90" t="s">
         <v>14</v>
       </c>
-      <c r="D85" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" ht="15">
-      <c r="D86"/>
-    </row>
-    <row r="87" spans="1:4" ht="15">
-      <c r="D87"/>
-    </row>
+      <c r="D90" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" ht="15"/>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:E85">
-    <sortCondition ref="A3:A85"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H90">
+    <sortCondition ref="A2:A90"/>
   </sortState>
   <hyperlinks>
     <hyperlink ref="A6" r:id="rId1" xr:uid="{9C9D4773-DBCF-4009-B4B9-68BFDE689EF3}"/>

--- a/SandBox/maps/Collaborators.xlsx
+++ b/SandBox/maps/Collaborators.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25906"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26124"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="515" documentId="11_2783B361715DD81B2B2E30CD8B5EBE776678445D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1BB7E97-53B4-45CB-A77E-238887486BBE}"/>
+  <xr:revisionPtr revIDLastSave="593" documentId="11_2783B361715DD81B2B2E30CD8B5EBE776678445D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B973B97-51F7-437D-B836-7921EDA20B62}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="236">
   <si>
     <t>Institution</t>
   </si>
@@ -615,6 +615,15 @@
     <t xml:space="preserve">Canada </t>
   </si>
   <si>
+    <t>Zayed University</t>
+  </si>
+  <si>
+    <t>Dubai</t>
+  </si>
+  <si>
+    <t>United Arab Emirates</t>
+  </si>
+  <si>
     <t>Ray Ryan</t>
   </si>
   <si>
@@ -637,13 +646,106 @@
   </si>
   <si>
     <t>Universidade Federal do Rio de Janeiro</t>
+  </si>
+  <si>
+    <t>Sorbonne Universite (Curie campus)</t>
+  </si>
+  <si>
+    <t>Bharat Tripathi</t>
+  </si>
+  <si>
+    <t>University of North Carolina at Chapel Hill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chapel Hill </t>
+  </si>
+  <si>
+    <t>India Institute of Technology Bombay</t>
+  </si>
+  <si>
+    <t>Mumbai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banaras Hindu University </t>
+  </si>
+  <si>
+    <t>Varanasi</t>
+  </si>
+  <si>
+    <t>KU Leuven</t>
+  </si>
+  <si>
+    <t>Leuven</t>
+  </si>
+  <si>
+    <t>James Cruickshank</t>
+  </si>
+  <si>
+    <t>University of Tokyo</t>
+  </si>
+  <si>
+    <t>Tokyo</t>
+  </si>
+  <si>
+    <t>Japan</t>
+  </si>
+  <si>
+    <t>Queen Mary University of London</t>
+  </si>
+  <si>
+    <t>Mary Immaculate College Baghdad</t>
+  </si>
+  <si>
+    <t>Thurles</t>
+  </si>
+  <si>
+    <t>Middle Technical University</t>
+  </si>
+  <si>
+    <t>Baghdad</t>
+  </si>
+  <si>
+    <t>Iraq</t>
+  </si>
+  <si>
+    <t>Lancaster University</t>
+  </si>
+  <si>
+    <t>Lancaster</t>
+  </si>
+  <si>
+    <t>ELTE Eotvos Lorand University</t>
+  </si>
+  <si>
+    <t>Budapest</t>
+  </si>
+  <si>
+    <t>Hungary</t>
+  </si>
+  <si>
+    <t>Universidad Austral de Chile</t>
+  </si>
+  <si>
+    <t>Valdvia</t>
+  </si>
+  <si>
+    <t>Chile</t>
+  </si>
+  <si>
+    <t>Kastamonu University</t>
+  </si>
+  <si>
+    <t>Kastamonu</t>
+  </si>
+  <si>
+    <t>Turkey</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -681,6 +783,11 @@
       <name val="Gotham"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF222222"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -717,7 +824,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -731,6 +838,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1045,7 +1153,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H103"/>
+  <dimension ref="A1:H118"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="36.42578125" customWidth="1"/>
@@ -2450,64 +2558,274 @@
     </row>
     <row r="100" spans="1:5" ht="15">
       <c r="A100" t="s">
+        <v>194</v>
+      </c>
+      <c r="B100" t="s">
+        <v>195</v>
+      </c>
+      <c r="C100" t="s">
+        <v>196</v>
+      </c>
+      <c r="D100" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="15">
+      <c r="A101" t="s">
         <v>128</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B101" t="s">
         <v>19</v>
       </c>
-      <c r="C100" t="s">
+      <c r="C101" t="s">
         <v>20</v>
       </c>
-      <c r="D100" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" ht="15">
-      <c r="A101" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="C101" s="3" t="s">
+      <c r="D101" t="s">
         <v>197</v>
       </c>
-      <c r="D101" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="E101" s="4"/>
     </row>
     <row r="102" spans="1:5" ht="15">
-      <c r="A102" t="s">
+      <c r="A102" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="C102" t="s">
+      <c r="C102" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="D102" t="s">
-        <v>194</v>
-      </c>
+      <c r="D102" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="E102" s="4"/>
     </row>
     <row r="103" spans="1:5" ht="15">
       <c r="A103" t="s">
         <v>201</v>
       </c>
       <c r="B103" t="s">
+        <v>202</v>
+      </c>
+      <c r="C103" t="s">
+        <v>203</v>
+      </c>
+      <c r="D103" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" ht="15">
+      <c r="A104" t="s">
+        <v>204</v>
+      </c>
+      <c r="B104" t="s">
         <v>24</v>
       </c>
-      <c r="C103" t="s">
+      <c r="C104" t="s">
         <v>25</v>
       </c>
-      <c r="D103" t="s">
-        <v>194</v>
+      <c r="D104" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" ht="15">
+      <c r="A105" t="s">
+        <v>205</v>
+      </c>
+      <c r="B105" t="s">
+        <v>80</v>
+      </c>
+      <c r="C105" t="s">
+        <v>68</v>
+      </c>
+      <c r="D105" s="5" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" ht="15">
+      <c r="A106" t="s">
+        <v>207</v>
+      </c>
+      <c r="B106" t="s">
+        <v>208</v>
+      </c>
+      <c r="C106" t="s">
+        <v>6</v>
+      </c>
+      <c r="D106" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" ht="15">
+      <c r="A107" t="s">
+        <v>209</v>
+      </c>
+      <c r="B107" t="s">
+        <v>210</v>
+      </c>
+      <c r="C107" t="s">
+        <v>165</v>
+      </c>
+      <c r="D107" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" ht="15">
+      <c r="A108" t="s">
+        <v>211</v>
+      </c>
+      <c r="B108" t="s">
+        <v>212</v>
+      </c>
+      <c r="C108" t="s">
+        <v>165</v>
+      </c>
+      <c r="D108" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" ht="15">
+      <c r="A109" t="s">
+        <v>213</v>
+      </c>
+      <c r="B109" t="s">
+        <v>214</v>
+      </c>
+      <c r="C109" t="s">
+        <v>125</v>
+      </c>
+      <c r="D109" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" ht="15">
+      <c r="A110" t="s">
+        <v>216</v>
+      </c>
+      <c r="B110" t="s">
+        <v>217</v>
+      </c>
+      <c r="C110" t="s">
+        <v>218</v>
+      </c>
+      <c r="D110" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" ht="15">
+      <c r="A111" t="s">
+        <v>219</v>
+      </c>
+      <c r="B111" t="s">
+        <v>28</v>
+      </c>
+      <c r="C111" t="s">
+        <v>17</v>
+      </c>
+      <c r="D111" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" ht="15">
+      <c r="A112" t="s">
+        <v>220</v>
+      </c>
+      <c r="B112" t="s">
+        <v>221</v>
+      </c>
+      <c r="C112" t="s">
+        <v>20</v>
+      </c>
+      <c r="D112" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" ht="15">
+      <c r="A113" t="s">
+        <v>222</v>
+      </c>
+      <c r="B113" t="s">
+        <v>223</v>
+      </c>
+      <c r="C113" t="s">
+        <v>224</v>
+      </c>
+      <c r="D113" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" ht="15">
+      <c r="A114" t="s">
+        <v>225</v>
+      </c>
+      <c r="B114" t="s">
+        <v>226</v>
+      </c>
+      <c r="C114" t="s">
+        <v>17</v>
+      </c>
+      <c r="D114" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" ht="15">
+      <c r="A115" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B115" t="s">
+        <v>228</v>
+      </c>
+      <c r="C115" t="s">
+        <v>229</v>
+      </c>
+      <c r="D115" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" ht="15">
+      <c r="A116" t="s">
+        <v>230</v>
+      </c>
+      <c r="B116" t="s">
+        <v>231</v>
+      </c>
+      <c r="C116" t="s">
+        <v>232</v>
+      </c>
+      <c r="D116" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" ht="15">
+      <c r="A117" t="s">
+        <v>233</v>
+      </c>
+      <c r="B117" t="s">
+        <v>234</v>
+      </c>
+      <c r="C117" t="s">
+        <v>235</v>
+      </c>
+      <c r="D117" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" ht="15">
+      <c r="A118" t="s">
+        <v>191</v>
+      </c>
+      <c r="B118" t="s">
+        <v>192</v>
+      </c>
+      <c r="C118" t="s">
+        <v>193</v>
+      </c>
+      <c r="D118" t="s">
+        <v>215</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D103">
-    <sortCondition ref="D2:D103"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D104">
+    <sortCondition ref="D2:D104"/>
   </sortState>
   <hyperlinks>
     <hyperlink ref="A80" r:id="rId1" xr:uid="{9C9D4773-DBCF-4009-B4B9-68BFDE689EF3}"/>

--- a/SandBox/maps/Collaborators.xlsx
+++ b/SandBox/maps/Collaborators.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26124"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="593" documentId="11_2783B361715DD81B2B2E30CD8B5EBE776678445D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B973B97-51F7-437D-B836-7921EDA20B62}"/>
+  <xr:revisionPtr revIDLastSave="595" documentId="11_2783B361715DD81B2B2E30CD8B5EBE776678445D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C053F4B8-3072-4FB3-A4B0-667EDD591BE5}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -693,13 +693,13 @@
     <t>Queen Mary University of London</t>
   </si>
   <si>
-    <t>Mary Immaculate College Baghdad</t>
+    <t>Mary Immaculate College</t>
   </si>
   <si>
     <t>Thurles</t>
   </si>
   <si>
-    <t>Middle Technical University</t>
+    <t>Middle Technical University Baghdad</t>
   </si>
   <si>
     <t>Baghdad</t>

--- a/SandBox/maps/Collaborators.xlsx
+++ b/SandBox/maps/Collaborators.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26124"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="595" documentId="11_2783B361715DD81B2B2E30CD8B5EBE776678445D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C053F4B8-3072-4FB3-A4B0-667EDD591BE5}"/>
+  <xr:revisionPtr revIDLastSave="619" documentId="11_2783B361715DD81B2B2E30CD8B5EBE776678445D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FE7822E-1B3C-4E0C-93A6-26E47E220259}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="242">
   <si>
     <t>Institution</t>
   </si>
@@ -739,6 +739,24 @@
   </si>
   <si>
     <t>Turkey</t>
+  </si>
+  <si>
+    <t>Valentina Balbi</t>
+  </si>
+  <si>
+    <t>Milano</t>
+  </si>
+  <si>
+    <t>University of Notre Dame</t>
+  </si>
+  <si>
+    <t>South Bend</t>
+  </si>
+  <si>
+    <t>TU Dresden</t>
+  </si>
+  <si>
+    <t>dresden</t>
   </si>
 </sst>
 </file>
@@ -824,7 +842,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -839,6 +857,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1153,7 +1172,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H118"/>
+  <dimension ref="A1:H122"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="36.42578125" customWidth="1"/>
@@ -1292,7 +1311,7 @@
       <c r="C9" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="8" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1306,7 +1325,7 @@
       <c r="C10" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="8" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1320,7 +1339,7 @@
       <c r="C11" t="s">
         <v>30</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="8" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1516,7 +1535,7 @@
       <c r="C25" t="s">
         <v>65</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" s="8" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1530,7 +1549,7 @@
       <c r="C26" t="s">
         <v>68</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" s="8" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1544,7 +1563,7 @@
       <c r="C27" t="s">
         <v>17</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" s="8" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1558,7 +1577,7 @@
       <c r="C28" t="s">
         <v>58</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" s="8" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1572,7 +1591,7 @@
       <c r="C29" t="s">
         <v>62</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" s="8" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2821,6 +2840,62 @@
       </c>
       <c r="D118" t="s">
         <v>215</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" ht="15">
+      <c r="A119" t="s">
+        <v>35</v>
+      </c>
+      <c r="B119" t="s">
+        <v>36</v>
+      </c>
+      <c r="C119" t="s">
+        <v>12</v>
+      </c>
+      <c r="D119" s="8" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" ht="15">
+      <c r="A120" t="s">
+        <v>97</v>
+      </c>
+      <c r="B120" t="s">
+        <v>237</v>
+      </c>
+      <c r="C120" t="s">
+        <v>34</v>
+      </c>
+      <c r="D120" s="8" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" ht="15">
+      <c r="A121" t="s">
+        <v>238</v>
+      </c>
+      <c r="B121" t="s">
+        <v>239</v>
+      </c>
+      <c r="C121" t="s">
+        <v>6</v>
+      </c>
+      <c r="D121" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" ht="15">
+      <c r="A122" t="s">
+        <v>240</v>
+      </c>
+      <c r="B122" t="s">
+        <v>241</v>
+      </c>
+      <c r="C122" t="s">
+        <v>170</v>
+      </c>
+      <c r="D122" s="8" t="s">
+        <v>160</v>
       </c>
     </row>
   </sheetData>

--- a/SandBox/maps/Collaborators.xlsx
+++ b/SandBox/maps/Collaborators.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26124"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="619" documentId="11_2783B361715DD81B2B2E30CD8B5EBE776678445D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FE7822E-1B3C-4E0C-93A6-26E47E220259}"/>
+  <xr:revisionPtr revIDLastSave="620" documentId="11_2783B361715DD81B2B2E30CD8B5EBE776678445D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{488A7BD3-ED62-49DC-A041-33DCB044B3B3}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -756,7 +756,7 @@
     <t>TU Dresden</t>
   </si>
   <si>
-    <t>dresden</t>
+    <t>Dresden</t>
   </si>
 </sst>
 </file>

--- a/SandBox/maps/Collaborators.xlsx
+++ b/SandBox/maps/Collaborators.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26124"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="620" documentId="11_2783B361715DD81B2B2E30CD8B5EBE776678445D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{488A7BD3-ED62-49DC-A041-33DCB044B3B3}"/>
+  <xr:revisionPtr revIDLastSave="653" documentId="11_2783B361715DD81B2B2E30CD8B5EBE776678445D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03A4B430-61B2-4805-969D-834C779FB33B}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="254">
   <si>
     <t>Institution</t>
   </si>
@@ -757,13 +757,49 @@
   </si>
   <si>
     <t>Dresden</t>
+  </si>
+  <si>
+    <t>John Newell</t>
+  </si>
+  <si>
+    <t>Purdue University</t>
+  </si>
+  <si>
+    <t>Indiana</t>
+  </si>
+  <si>
+    <t>St. Mary's University</t>
+  </si>
+  <si>
+    <t>Karolinska Institutet</t>
+  </si>
+  <si>
+    <t>Stockholm</t>
+  </si>
+  <si>
+    <t>Sweden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aristotle University of Thessaloniki </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thessaloniki </t>
+  </si>
+  <si>
+    <t>Greece</t>
+  </si>
+  <si>
+    <t>The Wharton School, University of Pennsylvania</t>
+  </si>
+  <si>
+    <t>Philadelphia</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -805,6 +841,13 @@
       <sz val="11"/>
       <color rgb="FF222222"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF444444"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -857,7 +900,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1172,7 +1215,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H122"/>
+  <dimension ref="A1:H128"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="36.42578125" customWidth="1"/>
@@ -1311,7 +1354,7 @@
       <c r="C9" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1325,7 +1368,7 @@
       <c r="C10" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1339,7 +1382,7 @@
       <c r="C11" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1535,7 +1578,7 @@
       <c r="C25" t="s">
         <v>65</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D25" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1549,7 +1592,7 @@
       <c r="C26" t="s">
         <v>68</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="D26" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1563,7 +1606,7 @@
       <c r="C27" t="s">
         <v>17</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="D27" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1577,7 +1620,7 @@
       <c r="C28" t="s">
         <v>58</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="D28" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1591,7 +1634,7 @@
       <c r="C29" t="s">
         <v>62</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="D29" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2852,7 +2895,7 @@
       <c r="C119" t="s">
         <v>12</v>
       </c>
-      <c r="D119" s="8" t="s">
+      <c r="D119" t="s">
         <v>236</v>
       </c>
     </row>
@@ -2866,7 +2909,7 @@
       <c r="C120" t="s">
         <v>34</v>
       </c>
-      <c r="D120" s="8" t="s">
+      <c r="D120" t="s">
         <v>236</v>
       </c>
     </row>
@@ -2894,8 +2937,92 @@
       <c r="C122" t="s">
         <v>170</v>
       </c>
-      <c r="D122" s="8" t="s">
+      <c r="D122" t="s">
         <v>160</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4">
+      <c r="A123" t="s">
+        <v>138</v>
+      </c>
+      <c r="B123" t="s">
+        <v>139</v>
+      </c>
+      <c r="C123" t="s">
+        <v>12</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" ht="15">
+      <c r="A124" t="s">
+        <v>243</v>
+      </c>
+      <c r="B124" t="s">
+        <v>244</v>
+      </c>
+      <c r="C124" t="s">
+        <v>6</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4">
+      <c r="A125" t="s">
+        <v>245</v>
+      </c>
+      <c r="B125" t="s">
+        <v>28</v>
+      </c>
+      <c r="C125" t="s">
+        <v>12</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4">
+      <c r="A126" t="s">
+        <v>246</v>
+      </c>
+      <c r="B126" t="s">
+        <v>247</v>
+      </c>
+      <c r="C126" t="s">
+        <v>248</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4">
+      <c r="A127" t="s">
+        <v>249</v>
+      </c>
+      <c r="B127" t="s">
+        <v>250</v>
+      </c>
+      <c r="C127" t="s">
+        <v>251</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" ht="15">
+      <c r="A128" t="s">
+        <v>252</v>
+      </c>
+      <c r="B128" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="C128" t="s">
+        <v>6</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>242</v>
       </c>
     </row>
   </sheetData>

--- a/SandBox/maps/Collaborators.xlsx
+++ b/SandBox/maps/Collaborators.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26124"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="653" documentId="11_2783B361715DD81B2B2E30CD8B5EBE776678445D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03A4B430-61B2-4805-969D-834C779FB33B}"/>
+  <xr:revisionPtr revIDLastSave="724" documentId="11_2783B361715DD81B2B2E30CD8B5EBE776678445D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25561DE8-E5A6-4C08-B143-E7932E33929F}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="278">
   <si>
     <t>Institution</t>
   </si>
@@ -793,6 +793,78 @@
   </si>
   <si>
     <t>Philadelphia</t>
+  </si>
+  <si>
+    <t>University of Bristol</t>
+  </si>
+  <si>
+    <t>Bristol</t>
+  </si>
+  <si>
+    <t>Andrew Simpkin</t>
+  </si>
+  <si>
+    <t>Harvard University</t>
+  </si>
+  <si>
+    <t>Columbia University</t>
+  </si>
+  <si>
+    <t>Emory University</t>
+  </si>
+  <si>
+    <t>Atlanta</t>
+  </si>
+  <si>
+    <t>University of Bath</t>
+  </si>
+  <si>
+    <t>Bath</t>
+  </si>
+  <si>
+    <t>Massey University</t>
+  </si>
+  <si>
+    <t>Palmerston North</t>
+  </si>
+  <si>
+    <t>New Zealand</t>
+  </si>
+  <si>
+    <t>University of Queensland</t>
+  </si>
+  <si>
+    <t>University of Oregon</t>
+  </si>
+  <si>
+    <t>Eugene</t>
+  </si>
+  <si>
+    <t>University of Michigan</t>
+  </si>
+  <si>
+    <t>Ann Arbor</t>
+  </si>
+  <si>
+    <t>Erasmus University Medical Center</t>
+  </si>
+  <si>
+    <t>Rotterdam</t>
+  </si>
+  <si>
+    <t>Netherlands</t>
+  </si>
+  <si>
+    <t>University of the West of England</t>
+  </si>
+  <si>
+    <t>Université Paris Cité</t>
+  </si>
+  <si>
+    <t>Université Rennes 2</t>
+  </si>
+  <si>
+    <t>Rennes</t>
   </si>
 </sst>
 </file>
@@ -885,7 +957,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -901,6 +973,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1215,7 +1288,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H128"/>
+  <dimension ref="A1:H144"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="36.42578125" customWidth="1"/>
@@ -2941,90 +3014,287 @@
         <v>160</v>
       </c>
     </row>
-    <row r="123" spans="1:4">
-      <c r="A123" t="s">
+    <row r="123" spans="1:4" s="9" customFormat="1" ht="15">
+      <c r="A123" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="C123" t="s">
+      <c r="C123" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D123" s="1" t="s">
+      <c r="D123" s="9" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="124" spans="1:4" ht="15">
-      <c r="A124" t="s">
+    <row r="124" spans="1:4" s="9" customFormat="1" ht="15">
+      <c r="A124" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B124" s="9" t="s">
         <v>244</v>
       </c>
-      <c r="C124" t="s">
+      <c r="C124" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D124" s="1" t="s">
+      <c r="D124" s="9" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="125" spans="1:4">
-      <c r="A125" t="s">
+    <row r="125" spans="1:4" s="9" customFormat="1" ht="15">
+      <c r="A125" s="9" t="s">
         <v>245</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B125" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C125" t="s">
+      <c r="C125" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D125" s="1" t="s">
+      <c r="D125" s="9" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="126" spans="1:4">
-      <c r="A126" t="s">
+    <row r="126" spans="1:4" s="9" customFormat="1" ht="15">
+      <c r="A126" s="9" t="s">
         <v>246</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B126" s="9" t="s">
         <v>247</v>
       </c>
-      <c r="C126" t="s">
+      <c r="C126" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="D126" s="1" t="s">
+      <c r="D126" s="9" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="127" spans="1:4">
-      <c r="A127" t="s">
+    <row r="127" spans="1:4" s="9" customFormat="1" ht="15">
+      <c r="A127" s="9" t="s">
         <v>249</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B127" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="C127" t="s">
+      <c r="C127" s="9" t="s">
         <v>251</v>
       </c>
-      <c r="D127" s="1" t="s">
+      <c r="D127" s="9" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="128" spans="1:4" ht="15">
-      <c r="A128" t="s">
+    <row r="128" spans="1:4" s="9" customFormat="1" ht="15">
+      <c r="A128" s="9" t="s">
         <v>252</v>
       </c>
       <c r="B128" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="C128" t="s">
+      <c r="C128" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D128" s="1" t="s">
+      <c r="D128" s="9" t="s">
         <v>242</v>
       </c>
     </row>
+    <row r="129" spans="1:4">
+      <c r="A129" t="s">
+        <v>254</v>
+      </c>
+      <c r="B129" t="s">
+        <v>255</v>
+      </c>
+      <c r="C129" t="s">
+        <v>12</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4">
+      <c r="A130" t="s">
+        <v>257</v>
+      </c>
+      <c r="B130" t="s">
+        <v>85</v>
+      </c>
+      <c r="C130" t="s">
+        <v>6</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4">
+      <c r="A131" t="s">
+        <v>258</v>
+      </c>
+      <c r="B131" t="s">
+        <v>5</v>
+      </c>
+      <c r="C131" t="s">
+        <v>6</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4">
+      <c r="A132" t="s">
+        <v>259</v>
+      </c>
+      <c r="B132" t="s">
+        <v>260</v>
+      </c>
+      <c r="C132" t="s">
+        <v>6</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4">
+      <c r="A133" t="s">
+        <v>261</v>
+      </c>
+      <c r="B133" t="s">
+        <v>262</v>
+      </c>
+      <c r="C133" t="s">
+        <v>12</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4">
+      <c r="A134" t="s">
+        <v>10</v>
+      </c>
+      <c r="B134" t="s">
+        <v>11</v>
+      </c>
+      <c r="C134" t="s">
+        <v>12</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" ht="15">
+      <c r="A135" t="s">
+        <v>263</v>
+      </c>
+      <c r="B135" t="s">
+        <v>264</v>
+      </c>
+      <c r="C135" t="s">
+        <v>265</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4">
+      <c r="A136" t="s">
+        <v>266</v>
+      </c>
+      <c r="B136" t="s">
+        <v>41</v>
+      </c>
+      <c r="C136" t="s">
+        <v>42</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4">
+      <c r="A137" t="s">
+        <v>267</v>
+      </c>
+      <c r="B137" t="s">
+        <v>268</v>
+      </c>
+      <c r="C137" t="s">
+        <v>6</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4">
+      <c r="A138" t="s">
+        <v>269</v>
+      </c>
+      <c r="B138" t="s">
+        <v>270</v>
+      </c>
+      <c r="C138" t="s">
+        <v>6</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4">
+      <c r="A139" t="s">
+        <v>271</v>
+      </c>
+      <c r="B139" t="s">
+        <v>272</v>
+      </c>
+      <c r="C139" t="s">
+        <v>273</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4">
+      <c r="A140" t="s">
+        <v>274</v>
+      </c>
+      <c r="B140" t="s">
+        <v>255</v>
+      </c>
+      <c r="C140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4">
+      <c r="A141" t="s">
+        <v>275</v>
+      </c>
+      <c r="B141" t="s">
+        <v>80</v>
+      </c>
+      <c r="C141" t="s">
+        <v>68</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4">
+      <c r="A142" t="s">
+        <v>276</v>
+      </c>
+      <c r="B142" t="s">
+        <v>277</v>
+      </c>
+      <c r="C142" t="s">
+        <v>68</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" ht="15"/>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D104">
     <sortCondition ref="D2:D104"/>

--- a/SandBox/maps/Collaborators.xlsx
+++ b/SandBox/maps/Collaborators.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26124"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="724" documentId="11_2783B361715DD81B2B2E30CD8B5EBE776678445D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25561DE8-E5A6-4C08-B143-E7932E33929F}"/>
+  <xr:revisionPtr revIDLastSave="757" documentId="11_2783B361715DD81B2B2E30CD8B5EBE776678445D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D06491DC-816E-4049-A93B-FD6FAAECDF4A}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="288">
   <si>
     <t>Institution</t>
   </si>
@@ -822,10 +822,10 @@
     <t>Bath</t>
   </si>
   <si>
-    <t>Massey University</t>
-  </si>
-  <si>
-    <t>Palmerston North</t>
+    <t>Massey University, Auckland</t>
+  </si>
+  <si>
+    <t>Auckland</t>
   </si>
   <si>
     <t>New Zealand</t>
@@ -865,6 +865,36 @@
   </si>
   <si>
     <t>Rennes</t>
+  </si>
+  <si>
+    <t>Bielefeld University</t>
+  </si>
+  <si>
+    <t>Bielefeld</t>
+  </si>
+  <si>
+    <t>Angela Carnevale</t>
+  </si>
+  <si>
+    <t>Università di Roma Tor Vergata</t>
+  </si>
+  <si>
+    <t>Roma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notre Dame </t>
+  </si>
+  <si>
+    <t>Bar-Ilan University</t>
+  </si>
+  <si>
+    <t>Bar-Ilan</t>
+  </si>
+  <si>
+    <t>Israel</t>
+  </si>
+  <si>
+    <t>DePaul University</t>
   </si>
 </sst>
 </file>
@@ -957,7 +987,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -973,7 +1003,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1288,7 +1317,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H144"/>
+  <dimension ref="A1:H148"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="36.42578125" customWidth="1"/>
@@ -3014,87 +3043,87 @@
         <v>160</v>
       </c>
     </row>
-    <row r="123" spans="1:4" s="9" customFormat="1" ht="15">
-      <c r="A123" s="9" t="s">
+    <row r="123" spans="1:4" ht="15">
+      <c r="A123" t="s">
         <v>138</v>
       </c>
-      <c r="B123" s="9" t="s">
+      <c r="B123" t="s">
         <v>139</v>
       </c>
-      <c r="C123" s="9" t="s">
+      <c r="C123" t="s">
         <v>12</v>
       </c>
-      <c r="D123" s="9" t="s">
+      <c r="D123" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="124" spans="1:4" s="9" customFormat="1" ht="15">
-      <c r="A124" s="9" t="s">
+    <row r="124" spans="1:4" ht="15">
+      <c r="A124" t="s">
         <v>243</v>
       </c>
-      <c r="B124" s="9" t="s">
+      <c r="B124" t="s">
         <v>244</v>
       </c>
-      <c r="C124" s="9" t="s">
+      <c r="C124" t="s">
         <v>6</v>
       </c>
-      <c r="D124" s="9" t="s">
+      <c r="D124" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="125" spans="1:4" s="9" customFormat="1" ht="15">
-      <c r="A125" s="9" t="s">
+    <row r="125" spans="1:4" ht="15">
+      <c r="A125" t="s">
         <v>245</v>
       </c>
-      <c r="B125" s="9" t="s">
+      <c r="B125" t="s">
         <v>28</v>
       </c>
-      <c r="C125" s="9" t="s">
+      <c r="C125" t="s">
         <v>12</v>
       </c>
-      <c r="D125" s="9" t="s">
+      <c r="D125" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="126" spans="1:4" s="9" customFormat="1" ht="15">
-      <c r="A126" s="9" t="s">
+    <row r="126" spans="1:4" ht="15">
+      <c r="A126" t="s">
         <v>246</v>
       </c>
-      <c r="B126" s="9" t="s">
+      <c r="B126" t="s">
         <v>247</v>
       </c>
-      <c r="C126" s="9" t="s">
+      <c r="C126" t="s">
         <v>248</v>
       </c>
-      <c r="D126" s="9" t="s">
+      <c r="D126" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="127" spans="1:4" s="9" customFormat="1" ht="15">
-      <c r="A127" s="9" t="s">
+    <row r="127" spans="1:4" ht="15">
+      <c r="A127" t="s">
         <v>249</v>
       </c>
-      <c r="B127" s="9" t="s">
+      <c r="B127" t="s">
         <v>250</v>
       </c>
-      <c r="C127" s="9" t="s">
+      <c r="C127" t="s">
         <v>251</v>
       </c>
-      <c r="D127" s="9" t="s">
+      <c r="D127" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="128" spans="1:4" s="9" customFormat="1" ht="15">
-      <c r="A128" s="9" t="s">
+    <row r="128" spans="1:4" ht="15">
+      <c r="A128" t="s">
         <v>252</v>
       </c>
       <c r="B128" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="C128" s="9" t="s">
+      <c r="C128" t="s">
         <v>6</v>
       </c>
-      <c r="D128" s="9" t="s">
+      <c r="D128" t="s">
         <v>242</v>
       </c>
     </row>
@@ -3294,7 +3323,90 @@
         <v>256</v>
       </c>
     </row>
-    <row r="144" spans="1:4" ht="15"/>
+    <row r="143" spans="1:4" ht="15">
+      <c r="A143" t="s">
+        <v>278</v>
+      </c>
+      <c r="B143" t="s">
+        <v>279</v>
+      </c>
+      <c r="C143" t="s">
+        <v>170</v>
+      </c>
+      <c r="D143" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" ht="15">
+      <c r="A144" t="s">
+        <v>281</v>
+      </c>
+      <c r="B144" t="s">
+        <v>282</v>
+      </c>
+      <c r="C144" t="s">
+        <v>34</v>
+      </c>
+      <c r="D144" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" ht="15">
+      <c r="A145" t="s">
+        <v>97</v>
+      </c>
+      <c r="B145" t="s">
+        <v>237</v>
+      </c>
+      <c r="C145" t="s">
+        <v>34</v>
+      </c>
+      <c r="D145" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" ht="15">
+      <c r="A146" t="s">
+        <v>238</v>
+      </c>
+      <c r="B146" t="s">
+        <v>283</v>
+      </c>
+      <c r="C146" t="s">
+        <v>6</v>
+      </c>
+      <c r="D146" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" ht="15">
+      <c r="A147" t="s">
+        <v>284</v>
+      </c>
+      <c r="B147" t="s">
+        <v>285</v>
+      </c>
+      <c r="C147" t="s">
+        <v>286</v>
+      </c>
+      <c r="D147" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" ht="15">
+      <c r="A148" t="s">
+        <v>287</v>
+      </c>
+      <c r="B148" t="s">
+        <v>141</v>
+      </c>
+      <c r="C148" t="s">
+        <v>6</v>
+      </c>
+      <c r="D148" t="s">
+        <v>280</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D104">
     <sortCondition ref="D2:D104"/>

--- a/SandBox/maps/Collaborators.xlsx
+++ b/SandBox/maps/Collaborators.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26124"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="757" documentId="11_2783B361715DD81B2B2E30CD8B5EBE776678445D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D06491DC-816E-4049-A93B-FD6FAAECDF4A}"/>
+  <xr:revisionPtr revIDLastSave="784" documentId="11_2783B361715DD81B2B2E30CD8B5EBE776678445D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DF8C843-0A93-4C85-86AB-ED0BF33D9DB6}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="299">
   <si>
     <t>Institution</t>
   </si>
@@ -895,6 +895,39 @@
   </si>
   <si>
     <t>DePaul University</t>
+  </si>
+  <si>
+    <t>Queen's University Belfast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Belfast </t>
+  </si>
+  <si>
+    <t>N. Ireland</t>
+  </si>
+  <si>
+    <t>Aisling McCluskey</t>
+  </si>
+  <si>
+    <t>Marquette University</t>
+  </si>
+  <si>
+    <t>Milwaukee, Wisconsin</t>
+  </si>
+  <si>
+    <t>University of New Brunswick</t>
+  </si>
+  <si>
+    <t>Fredericton</t>
+  </si>
+  <si>
+    <t>University of Auckland</t>
+  </si>
+  <si>
+    <t>University of Birmingham</t>
+  </si>
+  <si>
+    <t>Birmingham</t>
   </si>
 </sst>
 </file>
@@ -987,7 +1020,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1003,6 +1036,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1317,7 +1351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H148"/>
+  <dimension ref="A1:H153"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="36.42578125" customWidth="1"/>
@@ -3407,6 +3441,76 @@
         <v>280</v>
       </c>
     </row>
+    <row r="149" spans="1:4" ht="15">
+      <c r="A149" t="s">
+        <v>288</v>
+      </c>
+      <c r="B149" t="s">
+        <v>289</v>
+      </c>
+      <c r="C149" t="s">
+        <v>290</v>
+      </c>
+      <c r="D149" s="5" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" ht="15">
+      <c r="A150" t="s">
+        <v>292</v>
+      </c>
+      <c r="B150" t="s">
+        <v>293</v>
+      </c>
+      <c r="C150" t="s">
+        <v>6</v>
+      </c>
+      <c r="D150" s="9" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" ht="15">
+      <c r="A151" t="s">
+        <v>294</v>
+      </c>
+      <c r="B151" t="s">
+        <v>295</v>
+      </c>
+      <c r="C151" t="s">
+        <v>193</v>
+      </c>
+      <c r="D151" s="5" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" ht="15">
+      <c r="A152" t="s">
+        <v>296</v>
+      </c>
+      <c r="B152" t="s">
+        <v>264</v>
+      </c>
+      <c r="C152" t="s">
+        <v>265</v>
+      </c>
+      <c r="D152" s="5" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" ht="15">
+      <c r="A153" t="s">
+        <v>297</v>
+      </c>
+      <c r="B153" t="s">
+        <v>298</v>
+      </c>
+      <c r="C153" t="s">
+        <v>12</v>
+      </c>
+      <c r="D153" s="5" t="s">
+        <v>291</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D104">
     <sortCondition ref="D2:D104"/>

--- a/SandBox/maps/Collaborators.xlsx
+++ b/SandBox/maps/Collaborators.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26124"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="784" documentId="11_2783B361715DD81B2B2E30CD8B5EBE776678445D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DF8C843-0A93-4C85-86AB-ED0BF33D9DB6}"/>
+  <xr:revisionPtr revIDLastSave="821" documentId="11_2783B361715DD81B2B2E30CD8B5EBE776678445D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9585045-193F-4FA6-A592-78FAFE8071AB}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="314">
   <si>
     <t>Institution</t>
   </si>
@@ -928,6 +928,51 @@
   </si>
   <si>
     <t>Birmingham</t>
+  </si>
+  <si>
+    <t>Ruhr-Universität Bochum</t>
+  </si>
+  <si>
+    <t>Bochum</t>
+  </si>
+  <si>
+    <t>Götz Pfeiffer</t>
+  </si>
+  <si>
+    <t>Universität Stuttgart</t>
+  </si>
+  <si>
+    <t>Stuttgart</t>
+  </si>
+  <si>
+    <t>Université de Picardie Jules Verne</t>
+  </si>
+  <si>
+    <t>Amiens</t>
+  </si>
+  <si>
+    <t>National Science Foundation</t>
+  </si>
+  <si>
+    <t>Alexandria</t>
+  </si>
+  <si>
+    <t>RWTH Aachen</t>
+  </si>
+  <si>
+    <t>Aachen</t>
+  </si>
+  <si>
+    <t>University of Wolverhampton</t>
+  </si>
+  <si>
+    <t>Wolverhampton</t>
+  </si>
+  <si>
+    <t>University of St Andrews</t>
+  </si>
+  <si>
+    <t>St Andrews</t>
   </si>
 </sst>
 </file>
@@ -1020,7 +1065,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1036,7 +1081,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1351,7 +1395,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H153"/>
+  <dimension ref="A1:H161"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="36.42578125" customWidth="1"/>
@@ -3465,7 +3509,7 @@
       <c r="C150" t="s">
         <v>6</v>
       </c>
-      <c r="D150" s="9" t="s">
+      <c r="D150" t="s">
         <v>291</v>
       </c>
     </row>
@@ -3509,6 +3553,118 @@
       </c>
       <c r="D153" s="5" t="s">
         <v>291</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" ht="15">
+      <c r="A154" t="s">
+        <v>299</v>
+      </c>
+      <c r="B154" t="s">
+        <v>300</v>
+      </c>
+      <c r="C154" t="s">
+        <v>170</v>
+      </c>
+      <c r="D154" s="5" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" ht="15">
+      <c r="A155" t="s">
+        <v>302</v>
+      </c>
+      <c r="B155" t="s">
+        <v>303</v>
+      </c>
+      <c r="C155" t="s">
+        <v>170</v>
+      </c>
+      <c r="D155" s="5" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" ht="15">
+      <c r="A156" t="s">
+        <v>304</v>
+      </c>
+      <c r="B156" t="s">
+        <v>305</v>
+      </c>
+      <c r="C156" t="s">
+        <v>68</v>
+      </c>
+      <c r="D156" s="5" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" ht="15">
+      <c r="A157" t="s">
+        <v>132</v>
+      </c>
+      <c r="B157" t="s">
+        <v>133</v>
+      </c>
+      <c r="C157" t="s">
+        <v>6</v>
+      </c>
+      <c r="D157" s="5" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" ht="15">
+      <c r="A158" t="s">
+        <v>306</v>
+      </c>
+      <c r="B158" t="s">
+        <v>307</v>
+      </c>
+      <c r="C158" t="s">
+        <v>6</v>
+      </c>
+      <c r="D158" s="5" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" ht="15">
+      <c r="A159" t="s">
+        <v>308</v>
+      </c>
+      <c r="B159" t="s">
+        <v>309</v>
+      </c>
+      <c r="C159" t="s">
+        <v>170</v>
+      </c>
+      <c r="D159" s="5" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" ht="15">
+      <c r="A160" t="s">
+        <v>310</v>
+      </c>
+      <c r="B160" t="s">
+        <v>311</v>
+      </c>
+      <c r="C160" t="s">
+        <v>12</v>
+      </c>
+      <c r="D160" s="5" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" ht="15">
+      <c r="A161" t="s">
+        <v>312</v>
+      </c>
+      <c r="B161" t="s">
+        <v>313</v>
+      </c>
+      <c r="C161" t="s">
+        <v>12</v>
+      </c>
+      <c r="D161" s="5" t="s">
+        <v>301</v>
       </c>
     </row>
   </sheetData>
